--- a/Assets/Originals/Excels/Button/ButtonMessage.xlsx
+++ b/Assets/Originals/Excels/Button/ButtonMessage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\Button\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE323FA2-1FB1-4D0D-A56F-FA5C1A42AB74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF483F5F-AE11-4E45-BF0C-A558679AA6F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="27">
   <si>
     <t>number</t>
     <phoneticPr fontId="1"/>
@@ -108,6 +108,49 @@
   </si>
   <si>
     <t>SE</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>明るさ(ゲーム開始後に設定することを推奨)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Brightness (Recommended to adjust after starting the game)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>画面モード</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t xml:space="preserve">
+Screen mode</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>フルスクリーン</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t xml:space="preserve">
+Full screen</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ウィンドウ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Window</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>解像度</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t xml:space="preserve">
+Resolution</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -151,8 +194,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -436,7 +482,7 @@
   <dimension ref="A1:E102"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
-    <col min="2" max="2" width="17.5" customWidth="1"/>
+    <col min="2" max="2" width="37.25" customWidth="1"/>
     <col min="3" max="3" width="20.5" customWidth="1"/>
     <col min="4" max="4" width="16.5" customWidth="1"/>
     <col min="5" max="5" width="18.625" customWidth="1"/>
@@ -578,59 +624,89 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:5" ht="75">
       <c r="A9">
         <v>7</v>
       </c>
+      <c r="B9" t="s">
+        <v>17</v>
+      </c>
       <c r="C9">
-        <v>14</v>
+        <v>12</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>18</v>
       </c>
       <c r="E9">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="37.5">
       <c r="A10">
         <v>8</v>
       </c>
+      <c r="B10" t="s">
+        <v>19</v>
+      </c>
       <c r="C10">
-        <v>14</v>
+        <v>10</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>20</v>
       </c>
       <c r="E10">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="37.5">
       <c r="A11">
         <v>9</v>
       </c>
+      <c r="B11" t="s">
+        <v>21</v>
+      </c>
       <c r="C11">
-        <v>14</v>
+        <v>16</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>22</v>
       </c>
       <c r="E11">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
         <v>10</v>
       </c>
+      <c r="B12" t="s">
+        <v>23</v>
+      </c>
       <c r="C12">
-        <v>14</v>
+        <v>16</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="E12">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="37.5">
       <c r="A13">
         <v>11</v>
       </c>
+      <c r="B13" t="s">
+        <v>25</v>
+      </c>
       <c r="C13">
-        <v>14</v>
+        <v>10</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="E13">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:5">

--- a/Assets/Originals/Excels/Button/ButtonMessage.xlsx
+++ b/Assets/Originals/Excels/Button/ButtonMessage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\Button\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF483F5F-AE11-4E45-BF0C-A558679AA6F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08D6B019-7720-4F48-BCE1-18109D248A93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="51">
   <si>
     <t>number</t>
     <phoneticPr fontId="1"/>
@@ -151,6 +151,106 @@
   <si>
     <t xml:space="preserve">
 Resolution</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>操作説明</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Operation instructions</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>表示</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>View</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>非表示</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Hidden</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アイテム説明</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Item description</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>コンパス説明</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t xml:space="preserve">
+Compass description</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>日本語</t>
+    <rPh sb="0" eb="3">
+      <t>ニホンゴ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>日本語</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>English</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>感度</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>音量調整</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Volume</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>明るさ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Brightness</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>画面</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Screen</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>説明</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Explanation</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>言語</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Language</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -709,147 +809,225 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14" spans="1:5" ht="37.5">
       <c r="A14">
         <v>12</v>
       </c>
+      <c r="B14" t="s">
+        <v>27</v>
+      </c>
       <c r="C14">
-        <v>14</v>
+        <v>10</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>28</v>
       </c>
       <c r="E14">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
         <v>13</v>
       </c>
+      <c r="B15" t="s">
+        <v>29</v>
+      </c>
       <c r="C15">
-        <v>14</v>
+        <v>16</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>30</v>
       </c>
       <c r="E15">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
         <v>14</v>
       </c>
+      <c r="B16" t="s">
+        <v>31</v>
+      </c>
       <c r="C16">
-        <v>14</v>
+        <v>16</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="E16">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
         <v>15</v>
       </c>
+      <c r="B17" t="s">
+        <v>33</v>
+      </c>
       <c r="C17">
-        <v>14</v>
+        <v>10</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>34</v>
       </c>
       <c r="E17">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="56.25">
       <c r="A18">
         <v>16</v>
       </c>
+      <c r="B18" t="s">
+        <v>35</v>
+      </c>
       <c r="C18">
-        <v>14</v>
+        <v>10</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="E18">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
         <v>17</v>
       </c>
+      <c r="B19" t="s">
+        <v>37</v>
+      </c>
       <c r="C19">
-        <v>14</v>
+        <v>16</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>38</v>
       </c>
       <c r="E19">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
         <v>18</v>
       </c>
+      <c r="B20" t="s">
+        <v>39</v>
+      </c>
       <c r="C20">
-        <v>14</v>
+        <v>16</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>39</v>
       </c>
       <c r="E20">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
         <v>19</v>
       </c>
+      <c r="B21" t="s">
+        <v>40</v>
+      </c>
       <c r="C21">
+        <v>24</v>
+      </c>
+      <c r="D21" s="1" t="s">
         <v>14</v>
       </c>
       <c r="E21">
-        <v>14</v>
+        <v>24</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
         <v>20</v>
       </c>
+      <c r="B22" t="s">
+        <v>41</v>
+      </c>
       <c r="C22">
-        <v>14</v>
+        <v>24</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="E22">
-        <v>14</v>
+        <v>24</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
         <v>21</v>
       </c>
+      <c r="B23" t="s">
+        <v>43</v>
+      </c>
       <c r="C23">
-        <v>14</v>
+        <v>24</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>44</v>
       </c>
       <c r="E23">
-        <v>14</v>
+        <v>24</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
         <v>22</v>
       </c>
+      <c r="B24" t="s">
+        <v>45</v>
+      </c>
       <c r="C24">
-        <v>14</v>
+        <v>24</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>46</v>
       </c>
       <c r="E24">
-        <v>14</v>
+        <v>24</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
         <v>23</v>
       </c>
+      <c r="B25" t="s">
+        <v>47</v>
+      </c>
       <c r="C25">
-        <v>14</v>
+        <v>24</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>48</v>
       </c>
       <c r="E25">
-        <v>14</v>
+        <v>24</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
         <v>24</v>
       </c>
+      <c r="B26" t="s">
+        <v>49</v>
+      </c>
       <c r="C26">
-        <v>14</v>
+        <v>24</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>50</v>
       </c>
       <c r="E26">
-        <v>14</v>
+        <v>24</v>
       </c>
     </row>
     <row r="27" spans="1:5">

--- a/Assets/Originals/Excels/Button/ButtonMessage.xlsx
+++ b/Assets/Originals/Excels/Button/ButtonMessage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\Button\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08D6B019-7720-4F48-BCE1-18109D248A93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC620C88-D7E2-4DF0-9CA5-9F8E8FE33E25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="55">
   <si>
     <t>number</t>
     <phoneticPr fontId="1"/>
@@ -251,6 +251,22 @@
   </si>
   <si>
     <t>Language</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>はい</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>いいえ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Yes</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>No</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1034,22 +1050,34 @@
       <c r="A27">
         <v>25</v>
       </c>
+      <c r="B27" t="s">
+        <v>51</v>
+      </c>
       <c r="C27">
-        <v>14</v>
+        <v>32</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>53</v>
       </c>
       <c r="E27">
-        <v>14</v>
+        <v>32</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
         <v>26</v>
       </c>
+      <c r="B28" t="s">
+        <v>52</v>
+      </c>
       <c r="C28">
-        <v>14</v>
+        <v>32</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>54</v>
       </c>
       <c r="E28">
-        <v>14</v>
+        <v>32</v>
       </c>
     </row>
     <row r="29" spans="1:5">

--- a/Assets/Originals/Excels/Button/ButtonMessage.xlsx
+++ b/Assets/Originals/Excels/Button/ButtonMessage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\Button\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC620C88-D7E2-4DF0-9CA5-9F8E8FE33E25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D41709FD-2813-474D-BFA6-730A03E250F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="90">
   <si>
     <t>number</t>
     <phoneticPr fontId="1"/>
@@ -267,6 +267,223 @@
   </si>
   <si>
     <t>No</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>memo</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>OptionPanel内の各戻るボタン</t>
+    <rPh sb="11" eb="12">
+      <t>ナイ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>カク</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>モド</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>MouseSensitivityPanel内</t>
+    <rPh sb="21" eb="22">
+      <t>ナイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ExplanationPanel内</t>
+    <rPh sb="16" eb="17">
+      <t>ナイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>感度ボタン</t>
+    <rPh sb="0" eb="2">
+      <t>カンド</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>音量調整ボタン</t>
+    <rPh sb="0" eb="2">
+      <t>オンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>明るさボタン</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>OpeningScene内のプレイヤー名入力後の選択肢</t>
+    <rPh sb="12" eb="13">
+      <t>ナイ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>メイ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>アト</t>
+    </rPh>
+    <rPh sb="24" eb="27">
+      <t>センタクシ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ReturnToTitlePanel内</t>
+    <rPh sb="18" eb="19">
+      <t>ナイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>BrightnessAdjustmentPanel内</t>
+    <rPh sb="25" eb="26">
+      <t>ナイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ドキュメント</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Document</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ViewItemsPanel内</t>
+    <rPh sb="14" eb="15">
+      <t>ナイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>戻る</t>
+  </si>
+  <si>
+    <t>ミステリーアイテム</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>MysteryItem</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>続ける</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Continue</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>PausePanel内</t>
+    <rPh sb="10" eb="11">
+      <t>ナイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アイテム確認</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Item confirmation</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>タイトル画面・PausePanel内</t>
+    <rPh sb="4" eb="6">
+      <t>ガメン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>タイトルへ戻る</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Return to title</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ViewItemsPanel内とGoalPanel内とStageAndDifficultyLevelChoosePanel内</t>
+    <rPh sb="14" eb="15">
+      <t>ナイ</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>ナイ</t>
+    </rPh>
+    <rPh sb="61" eb="62">
+      <t>ナイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>第一迷宮</t>
+    <rPh sb="0" eb="1">
+      <t>ダイ</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>イチ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>メイキュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>First labyrinth</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>デモ用</t>
+    <rPh sb="2" eb="3">
+      <t>ヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>夢想</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>夢幻</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>悪夢</t>
+    <rPh sb="0" eb="2">
+      <t>アクム</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Reverie</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Phantasm</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Nightmare</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>DifficultyLevelChoosePanel内</t>
+    <rPh sb="26" eb="27">
+      <t>ナイ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -595,16 +812,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E102"/>
+  <dimension ref="A1:F102"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="2" max="2" width="37.25" customWidth="1"/>
     <col min="3" max="3" width="20.5" customWidth="1"/>
     <col min="4" max="4" width="16.5" customWidth="1"/>
     <col min="5" max="5" width="18.625" customWidth="1"/>
+    <col min="6" max="6" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -620,8 +838,11 @@
       <c r="E1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:5">
+      <c r="F1" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
       <c r="A2">
         <v>0</v>
       </c>
@@ -638,7 +859,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:6" ht="75">
       <c r="A3">
         <v>1</v>
       </c>
@@ -654,8 +875,11 @@
       <c r="E3">
         <v>14</v>
       </c>
-    </row>
-    <row r="4" spans="1:5">
+      <c r="F3" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
       <c r="A4">
         <v>2</v>
       </c>
@@ -672,7 +896,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:6" ht="75">
       <c r="A5">
         <v>3</v>
       </c>
@@ -688,8 +912,11 @@
       <c r="E5">
         <v>24</v>
       </c>
-    </row>
-    <row r="6" spans="1:5">
+      <c r="F5" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="56.25">
       <c r="A6">
         <v>4</v>
       </c>
@@ -705,8 +932,11 @@
       <c r="E6">
         <v>14</v>
       </c>
-    </row>
-    <row r="7" spans="1:5">
+      <c r="F6" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
       <c r="A7">
         <v>5</v>
       </c>
@@ -723,7 +953,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:6">
       <c r="A8">
         <v>6</v>
       </c>
@@ -740,7 +970,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="75">
+    <row r="9" spans="1:6" ht="75">
       <c r="A9">
         <v>7</v>
       </c>
@@ -757,7 +987,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="37.5">
+    <row r="10" spans="1:6" ht="37.5">
       <c r="A10">
         <v>8</v>
       </c>
@@ -774,7 +1004,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="37.5">
+    <row r="11" spans="1:6" ht="37.5">
       <c r="A11">
         <v>9</v>
       </c>
@@ -791,7 +1021,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12" spans="1:6">
       <c r="A12">
         <v>10</v>
       </c>
@@ -808,7 +1038,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="37.5">
+    <row r="13" spans="1:6" ht="37.5">
       <c r="A13">
         <v>11</v>
       </c>
@@ -825,7 +1055,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="37.5">
+    <row r="14" spans="1:6" ht="56.25">
       <c r="A14">
         <v>12</v>
       </c>
@@ -841,8 +1071,11 @@
       <c r="E14">
         <v>10</v>
       </c>
-    </row>
-    <row r="15" spans="1:5">
+      <c r="F14" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="56.25">
       <c r="A15">
         <v>13</v>
       </c>
@@ -858,8 +1091,11 @@
       <c r="E15">
         <v>16</v>
       </c>
-    </row>
-    <row r="16" spans="1:5">
+      <c r="F15" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="56.25">
       <c r="A16">
         <v>14</v>
       </c>
@@ -875,8 +1111,11 @@
       <c r="E16">
         <v>16</v>
       </c>
-    </row>
-    <row r="17" spans="1:5">
+      <c r="F16" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
       <c r="A17">
         <v>15</v>
       </c>
@@ -893,7 +1132,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="56.25">
+    <row r="18" spans="1:6" ht="56.25">
       <c r="A18">
         <v>16</v>
       </c>
@@ -910,7 +1149,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="19" spans="1:5">
+    <row r="19" spans="1:6">
       <c r="A19">
         <v>17</v>
       </c>
@@ -927,7 +1166,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="20" spans="1:5">
+    <row r="20" spans="1:6">
       <c r="A20">
         <v>18</v>
       </c>
@@ -944,7 +1183,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="21" spans="1:5">
+    <row r="21" spans="1:6" ht="37.5">
       <c r="A21">
         <v>19</v>
       </c>
@@ -960,8 +1199,11 @@
       <c r="E21">
         <v>24</v>
       </c>
-    </row>
-    <row r="22" spans="1:5">
+      <c r="F21" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="37.5">
       <c r="A22">
         <v>20</v>
       </c>
@@ -977,8 +1219,11 @@
       <c r="E22">
         <v>24</v>
       </c>
-    </row>
-    <row r="23" spans="1:5">
+      <c r="F22" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="37.5">
       <c r="A23">
         <v>21</v>
       </c>
@@ -994,8 +1239,11 @@
       <c r="E23">
         <v>24</v>
       </c>
-    </row>
-    <row r="24" spans="1:5">
+      <c r="F23" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6">
       <c r="A24">
         <v>22</v>
       </c>
@@ -1012,7 +1260,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="25" spans="1:5">
+    <row r="25" spans="1:6">
       <c r="A25">
         <v>23</v>
       </c>
@@ -1029,7 +1277,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="26" spans="1:5">
+    <row r="26" spans="1:6">
       <c r="A26">
         <v>24</v>
       </c>
@@ -1046,7 +1294,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="27" spans="1:5">
+    <row r="27" spans="1:6" ht="112.5">
       <c r="A27">
         <v>25</v>
       </c>
@@ -1062,8 +1310,11 @@
       <c r="E27">
         <v>32</v>
       </c>
-    </row>
-    <row r="28" spans="1:5">
+      <c r="F27" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="112.5">
       <c r="A28">
         <v>26</v>
       </c>
@@ -1079,162 +1330,282 @@
       <c r="E28">
         <v>32</v>
       </c>
-    </row>
-    <row r="29" spans="1:5">
+      <c r="F28" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="56.25">
       <c r="A29">
         <v>27</v>
       </c>
+      <c r="B29" t="s">
+        <v>51</v>
+      </c>
       <c r="C29">
         <v>14</v>
       </c>
+      <c r="D29" s="1" t="s">
+        <v>53</v>
+      </c>
       <c r="E29">
         <v>14</v>
       </c>
-    </row>
-    <row r="30" spans="1:5">
+      <c r="F29" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="56.25">
       <c r="A30">
         <v>28</v>
       </c>
+      <c r="B30" t="s">
+        <v>52</v>
+      </c>
       <c r="C30">
         <v>14</v>
       </c>
+      <c r="D30" s="1" t="s">
+        <v>54</v>
+      </c>
       <c r="E30">
         <v>14</v>
       </c>
-    </row>
-    <row r="31" spans="1:5">
+      <c r="F30" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" ht="75">
       <c r="A31">
         <v>29</v>
       </c>
+      <c r="B31" t="s">
+        <v>43</v>
+      </c>
       <c r="C31">
-        <v>14</v>
+        <v>12</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>44</v>
       </c>
       <c r="E31">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
+        <v>12</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" ht="37.5">
       <c r="A32">
         <v>30</v>
       </c>
+      <c r="B32" t="s">
+        <v>65</v>
+      </c>
       <c r="C32">
         <v>14</v>
       </c>
+      <c r="D32" s="1" t="s">
+        <v>66</v>
+      </c>
       <c r="E32">
         <v>14</v>
       </c>
-    </row>
-    <row r="33" spans="1:5">
+      <c r="F32" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" ht="187.5">
       <c r="A33">
         <v>31</v>
       </c>
+      <c r="B33" t="s">
+        <v>11</v>
+      </c>
       <c r="C33">
         <v>14</v>
       </c>
+      <c r="D33" s="1" t="s">
+        <v>12</v>
+      </c>
       <c r="E33">
         <v>14</v>
       </c>
-    </row>
-    <row r="34" spans="1:5">
+      <c r="F33" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" ht="37.5">
       <c r="A34">
         <v>32</v>
       </c>
+      <c r="B34" t="s">
+        <v>69</v>
+      </c>
       <c r="C34">
         <v>14</v>
       </c>
+      <c r="D34" s="1" t="s">
+        <v>70</v>
+      </c>
       <c r="E34">
         <v>14</v>
       </c>
-    </row>
-    <row r="35" spans="1:5">
+      <c r="F34" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" ht="37.5">
       <c r="A35">
         <v>33</v>
       </c>
+      <c r="B35" t="s">
+        <v>71</v>
+      </c>
       <c r="C35">
         <v>14</v>
       </c>
+      <c r="D35" s="1" t="s">
+        <v>72</v>
+      </c>
       <c r="E35">
         <v>14</v>
       </c>
-    </row>
-    <row r="36" spans="1:5">
+      <c r="F35" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" ht="37.5">
       <c r="A36">
         <v>34</v>
       </c>
+      <c r="B36" t="s">
+        <v>74</v>
+      </c>
       <c r="C36">
         <v>14</v>
       </c>
+      <c r="D36" s="1" t="s">
+        <v>75</v>
+      </c>
       <c r="E36">
         <v>14</v>
       </c>
-    </row>
-    <row r="37" spans="1:5">
+      <c r="F36" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" ht="37.5">
       <c r="A37">
         <v>35</v>
       </c>
+      <c r="B37" t="s">
+        <v>77</v>
+      </c>
       <c r="C37">
         <v>14</v>
       </c>
+      <c r="D37" s="1" t="s">
+        <v>78</v>
+      </c>
       <c r="E37">
         <v>14</v>
       </c>
-    </row>
-    <row r="38" spans="1:5">
+      <c r="F37" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6">
       <c r="A38">
         <v>36</v>
       </c>
+      <c r="B38" t="s">
+        <v>80</v>
+      </c>
       <c r="C38">
-        <v>14</v>
+        <v>20</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>81</v>
       </c>
       <c r="E38">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
+        <v>20</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6">
       <c r="A39">
         <v>37</v>
       </c>
+      <c r="B39" t="s">
+        <v>83</v>
+      </c>
       <c r="C39">
         <v>14</v>
       </c>
+      <c r="D39" t="s">
+        <v>86</v>
+      </c>
       <c r="E39">
         <v>14</v>
       </c>
     </row>
-    <row r="40" spans="1:5">
+    <row r="40" spans="1:6">
       <c r="A40">
         <v>38</v>
       </c>
+      <c r="B40" t="s">
+        <v>84</v>
+      </c>
       <c r="C40">
         <v>14</v>
       </c>
+      <c r="D40" t="s">
+        <v>87</v>
+      </c>
       <c r="E40">
         <v>14</v>
       </c>
     </row>
-    <row r="41" spans="1:5">
+    <row r="41" spans="1:6">
       <c r="A41">
         <v>39</v>
       </c>
+      <c r="B41" t="s">
+        <v>85</v>
+      </c>
       <c r="C41">
         <v>14</v>
       </c>
+      <c r="D41" t="s">
+        <v>88</v>
+      </c>
       <c r="E41">
         <v>14</v>
       </c>
     </row>
-    <row r="42" spans="1:5">
+    <row r="42" spans="1:6" ht="75">
       <c r="A42">
         <v>40</v>
       </c>
+      <c r="B42" t="s">
+        <v>68</v>
+      </c>
       <c r="C42">
-        <v>14</v>
+        <v>20</v>
+      </c>
+      <c r="D42" t="s">
+        <v>12</v>
       </c>
       <c r="E42">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
+        <v>16</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6">
       <c r="A43">
         <v>41</v>
       </c>
@@ -1245,7 +1616,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="44" spans="1:5">
+    <row r="44" spans="1:6">
       <c r="A44">
         <v>42</v>
       </c>
@@ -1256,7 +1627,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="45" spans="1:5">
+    <row r="45" spans="1:6">
       <c r="A45">
         <v>43</v>
       </c>
@@ -1267,7 +1638,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="46" spans="1:5">
+    <row r="46" spans="1:6">
       <c r="A46">
         <v>44</v>
       </c>
@@ -1278,7 +1649,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="47" spans="1:5">
+    <row r="47" spans="1:6">
       <c r="A47">
         <v>45</v>
       </c>
@@ -1289,7 +1660,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="48" spans="1:5">
+    <row r="48" spans="1:6">
       <c r="A48">
         <v>46</v>
       </c>

--- a/Assets/Originals/Excels/Button/ButtonMessage.xlsx
+++ b/Assets/Originals/Excels/Button/ButtonMessage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\Button\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D41709FD-2813-474D-BFA6-730A03E250F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F815135-BA65-4D9F-A19B-6504C2DEFED0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="94">
   <si>
     <t>number</t>
     <phoneticPr fontId="1"/>
@@ -484,6 +484,28 @@
     <rPh sb="26" eb="27">
       <t>ナイ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>PausePanel内・GameOverScene内</t>
+    <rPh sb="10" eb="11">
+      <t>ナイ</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>ナイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>リスタート</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>GameOverScene内</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Restart</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1494,7 +1516,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="37" spans="1:6" ht="37.5">
+    <row r="37" spans="1:6" ht="75">
       <c r="A37">
         <v>35</v>
       </c>
@@ -1511,7 +1533,7 @@
         <v>14</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>73</v>
+        <v>90</v>
       </c>
     </row>
     <row r="38" spans="1:6">
@@ -1605,15 +1627,24 @@
         <v>89</v>
       </c>
     </row>
-    <row r="43" spans="1:6">
+    <row r="43" spans="1:6" ht="37.5">
       <c r="A43">
         <v>41</v>
       </c>
+      <c r="B43" t="s">
+        <v>91</v>
+      </c>
       <c r="C43">
         <v>14</v>
       </c>
+      <c r="D43" t="s">
+        <v>93</v>
+      </c>
       <c r="E43">
         <v>14</v>
+      </c>
+      <c r="F43" s="1" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="44" spans="1:6">

--- a/Assets/Originals/Excels/Button/ButtonMessage.xlsx
+++ b/Assets/Originals/Excels/Button/ButtonMessage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\Button\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F815135-BA65-4D9F-A19B-6504C2DEFED0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0886D955-559E-450B-B8B1-F6A87648AE20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="99">
   <si>
     <t>number</t>
     <phoneticPr fontId="1"/>
@@ -506,6 +506,30 @@
   </si>
   <si>
     <t>Restart</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>GameClearScene内</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ウィッシュリストは
+こちらをクリック！</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Click here 
+for the survey!</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アンケートは
+こちらをクリック！</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Click here for 
+your Wishlist!</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1647,37 +1671,58 @@
         <v>92</v>
       </c>
     </row>
-    <row r="44" spans="1:6">
+    <row r="44" spans="1:6" ht="56.25">
       <c r="A44">
         <v>42</v>
       </c>
+      <c r="B44" t="s">
+        <v>77</v>
+      </c>
       <c r="C44">
-        <v>14</v>
+        <v>20</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>78</v>
       </c>
       <c r="E44">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6">
+        <v>20</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" ht="37.5">
       <c r="A45">
         <v>43</v>
       </c>
+      <c r="B45" s="1" t="s">
+        <v>97</v>
+      </c>
       <c r="C45">
-        <v>14</v>
+        <v>12</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>96</v>
       </c>
       <c r="E45">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" ht="37.5">
       <c r="A46">
         <v>44</v>
       </c>
+      <c r="B46" s="1" t="s">
+        <v>95</v>
+      </c>
       <c r="C46">
-        <v>14</v>
+        <v>12</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>98</v>
       </c>
       <c r="E46">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="47" spans="1:6">

--- a/Assets/Originals/Excels/Button/ButtonMessage.xlsx
+++ b/Assets/Originals/Excels/Button/ButtonMessage.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\Button\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0886D955-559E-450B-B8B1-F6A87648AE20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA62A422-D169-405B-AA81-325228461A2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1243,7 +1243,7 @@
         <v>14</v>
       </c>
       <c r="E21">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>59</v>
@@ -1263,7 +1263,7 @@
         <v>42</v>
       </c>
       <c r="E22">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>60</v>
@@ -1283,7 +1283,7 @@
         <v>44</v>
       </c>
       <c r="E23">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>61</v>
@@ -1303,7 +1303,7 @@
         <v>46</v>
       </c>
       <c r="E24">
-        <v>24</v>
+        <v>18</v>
       </c>
     </row>
     <row r="25" spans="1:6">
@@ -1320,7 +1320,7 @@
         <v>48</v>
       </c>
       <c r="E25">
-        <v>24</v>
+        <v>18</v>
       </c>
     </row>
     <row r="26" spans="1:6">
@@ -1337,7 +1337,7 @@
         <v>50</v>
       </c>
       <c r="E26">
-        <v>24</v>
+        <v>18</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="112.5">

--- a/Assets/Originals/Excels/Button/ButtonMessage.xlsx
+++ b/Assets/Originals/Excels/Button/ButtonMessage.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\Button\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA62A422-D169-405B-AA81-325228461A2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8FFDBB3-D61E-4E25-A11E-AEC0888E1347}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -429,30 +429,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>第一迷宮</t>
-    <rPh sb="0" eb="1">
-      <t>ダイ</t>
-    </rPh>
-    <rPh sb="1" eb="2">
-      <t>イチ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>メイキュウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>First labyrinth</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>デモ用</t>
-    <rPh sb="2" eb="3">
-      <t>ヨウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>夢想</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -530,6 +506,18 @@
   <si>
     <t>Click here for 
 your Wishlist!</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>幽獄迷宮</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Phantom Prison Labyrinth</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ステージ1</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -865,7 +853,7 @@
     <col min="3" max="3" width="20.5" customWidth="1"/>
     <col min="4" max="4" width="16.5" customWidth="1"/>
     <col min="5" max="5" width="18.625" customWidth="1"/>
-    <col min="6" max="6" width="9" style="1"/>
+    <col min="6" max="6" width="12.375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -1557,27 +1545,27 @@
         <v>14</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" ht="37.5">
       <c r="A38">
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="C38">
         <v>20</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>81</v>
+        <v>97</v>
       </c>
       <c r="E38">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>82</v>
+        <v>98</v>
       </c>
     </row>
     <row r="39" spans="1:6">
@@ -1585,13 +1573,13 @@
         <v>37</v>
       </c>
       <c r="B39" t="s">
+        <v>80</v>
+      </c>
+      <c r="C39">
+        <v>14</v>
+      </c>
+      <c r="D39" t="s">
         <v>83</v>
-      </c>
-      <c r="C39">
-        <v>14</v>
-      </c>
-      <c r="D39" t="s">
-        <v>86</v>
       </c>
       <c r="E39">
         <v>14</v>
@@ -1602,13 +1590,13 @@
         <v>38</v>
       </c>
       <c r="B40" t="s">
+        <v>81</v>
+      </c>
+      <c r="C40">
+        <v>14</v>
+      </c>
+      <c r="D40" t="s">
         <v>84</v>
-      </c>
-      <c r="C40">
-        <v>14</v>
-      </c>
-      <c r="D40" t="s">
-        <v>87</v>
       </c>
       <c r="E40">
         <v>14</v>
@@ -1619,13 +1607,13 @@
         <v>39</v>
       </c>
       <c r="B41" t="s">
+        <v>82</v>
+      </c>
+      <c r="C41">
+        <v>14</v>
+      </c>
+      <c r="D41" t="s">
         <v>85</v>
-      </c>
-      <c r="C41">
-        <v>14</v>
-      </c>
-      <c r="D41" t="s">
-        <v>88</v>
       </c>
       <c r="E41">
         <v>14</v>
@@ -1648,7 +1636,7 @@
         <v>16</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
     </row>
     <row r="43" spans="1:6" ht="37.5">
@@ -1656,19 +1644,19 @@
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C43">
         <v>14</v>
       </c>
       <c r="D43" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="E43">
         <v>14</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="44" spans="1:6" ht="56.25">
@@ -1688,7 +1676,7 @@
         <v>20</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="45" spans="1:6" ht="37.5">
@@ -1696,13 +1684,13 @@
         <v>43</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C45">
         <v>12</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="E45">
         <v>12</v>
@@ -1713,13 +1701,13 @@
         <v>44</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C46">
         <v>12</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="E46">
         <v>12</v>

--- a/Assets/Originals/Excels/Button/ButtonMessage.xlsx
+++ b/Assets/Originals/Excels/Button/ButtonMessage.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\Button\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8FFDBB3-D61E-4E25-A11E-AEC0888E1347}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72B37B0D-E6D9-4BE2-8E08-1503AF030E05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -509,15 +509,15 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
+    <t>Phantom Prison Labyrinth</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ステージ1</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
     <t>幽獄迷宮</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Phantom Prison Labyrinth</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ステージ1</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -849,7 +849,7 @@
   <dimension ref="A1:F102"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
-    <col min="2" max="2" width="37.25" customWidth="1"/>
+    <col min="2" max="2" width="51.25" customWidth="1"/>
     <col min="3" max="3" width="20.5" customWidth="1"/>
     <col min="4" max="4" width="16.5" customWidth="1"/>
     <col min="5" max="5" width="18.625" customWidth="1"/>
@@ -930,7 +930,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="75">
+    <row r="5" spans="1:6" ht="56.25">
       <c r="A5">
         <v>3</v>
       </c>
@@ -950,7 +950,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="56.25">
+    <row r="6" spans="1:6" ht="37.5">
       <c r="A6">
         <v>4</v>
       </c>
@@ -1089,7 +1089,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="56.25">
+    <row r="14" spans="1:6" ht="37.5">
       <c r="A14">
         <v>12</v>
       </c>
@@ -1109,7 +1109,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="56.25">
+    <row r="15" spans="1:6" ht="37.5">
       <c r="A15">
         <v>13</v>
       </c>
@@ -1129,7 +1129,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="56.25">
+    <row r="16" spans="1:6" ht="37.5">
       <c r="A16">
         <v>14</v>
       </c>
@@ -1217,7 +1217,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="37.5">
+    <row r="21" spans="1:6">
       <c r="A21">
         <v>19</v>
       </c>
@@ -1257,7 +1257,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="23" spans="1:6" ht="37.5">
+    <row r="23" spans="1:6">
       <c r="A23">
         <v>21</v>
       </c>
@@ -1328,7 +1328,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="27" spans="1:6" ht="112.5">
+    <row r="27" spans="1:6" ht="75">
       <c r="A27">
         <v>25</v>
       </c>
@@ -1348,7 +1348,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="28" spans="1:6" ht="112.5">
+    <row r="28" spans="1:6" ht="75">
       <c r="A28">
         <v>26</v>
       </c>
@@ -1368,7 +1368,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="29" spans="1:6" ht="56.25">
+    <row r="29" spans="1:6" ht="37.5">
       <c r="A29">
         <v>27</v>
       </c>
@@ -1388,7 +1388,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="30" spans="1:6" ht="56.25">
+    <row r="30" spans="1:6" ht="37.5">
       <c r="A30">
         <v>28</v>
       </c>
@@ -1408,7 +1408,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="31" spans="1:6" ht="75">
+    <row r="31" spans="1:6" ht="56.25">
       <c r="A31">
         <v>29</v>
       </c>
@@ -1448,7 +1448,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="33" spans="1:6" ht="187.5">
+    <row r="33" spans="1:6" ht="131.25">
       <c r="A33">
         <v>31</v>
       </c>
@@ -1553,19 +1553,19 @@
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C38">
         <v>20</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E38">
         <v>16</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="39" spans="1:6">
@@ -1619,7 +1619,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="42" spans="1:6" ht="75">
+    <row r="42" spans="1:6" ht="56.25">
       <c r="A42">
         <v>40</v>
       </c>
@@ -1659,7 +1659,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="44" spans="1:6" ht="56.25">
+    <row r="44" spans="1:6" ht="37.5">
       <c r="A44">
         <v>42</v>
       </c>

--- a/Assets/Originals/Excels/Button/ButtonMessage.xlsx
+++ b/Assets/Originals/Excels/Button/ButtonMessage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\Button\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72B37B0D-E6D9-4BE2-8E08-1503AF030E05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F65EF84-C6F8-4249-8CAE-E7D527479504}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -190,11 +190,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t xml:space="preserve">
-Compass description</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>日本語</t>
     <rPh sb="0" eb="3">
       <t>ニホンゴ</t>
@@ -518,6 +513,10 @@
   </si>
   <si>
     <t>幽獄迷宮</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Compass description</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -873,7 +872,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -910,7 +909,7 @@
         <v>14</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -947,7 +946,7 @@
         <v>24</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="37.5">
@@ -967,7 +966,7 @@
         <v>14</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -1103,10 +1102,10 @@
         <v>28</v>
       </c>
       <c r="E14">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="37.5">
@@ -1126,7 +1125,7 @@
         <v>16</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="37.5">
@@ -1146,7 +1145,7 @@
         <v>16</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -1166,7 +1165,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="56.25">
+    <row r="18" spans="1:6" ht="37.5">
       <c r="A18">
         <v>16</v>
       </c>
@@ -1177,10 +1176,10 @@
         <v>10</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>36</v>
+        <v>98</v>
       </c>
       <c r="E18">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -1188,13 +1187,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C19">
         <v>16</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E19">
         <v>16</v>
@@ -1205,13 +1204,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C20">
         <v>16</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E20">
         <v>16</v>
@@ -1222,7 +1221,7 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C21">
         <v>24</v>
@@ -1234,7 +1233,7 @@
         <v>18</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="37.5">
@@ -1242,19 +1241,19 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C22">
         <v>24</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E22">
         <v>18</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -1262,19 +1261,19 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C23">
         <v>24</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E23">
         <v>18</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -1282,13 +1281,13 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C24">
         <v>24</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E24">
         <v>18</v>
@@ -1299,13 +1298,13 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C25">
         <v>24</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E25">
         <v>18</v>
@@ -1316,13 +1315,13 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C26">
         <v>24</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E26">
         <v>18</v>
@@ -1333,19 +1332,19 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C27">
         <v>32</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E27">
         <v>32</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="75">
@@ -1353,19 +1352,19 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C28">
         <v>32</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E28">
         <v>32</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="37.5">
@@ -1373,19 +1372,19 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C29">
         <v>14</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E29">
         <v>14</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="37.5">
@@ -1393,19 +1392,19 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C30">
         <v>14</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E30">
         <v>14</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="56.25">
@@ -1413,19 +1412,19 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C31">
         <v>12</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E31">
         <v>12</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="37.5">
@@ -1433,19 +1432,19 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
+        <v>64</v>
+      </c>
+      <c r="C32">
+        <v>14</v>
+      </c>
+      <c r="D32" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="C32">
-        <v>14</v>
-      </c>
-      <c r="D32" s="1" t="s">
+      <c r="E32">
+        <v>14</v>
+      </c>
+      <c r="F32" s="1" t="s">
         <v>66</v>
-      </c>
-      <c r="E32">
-        <v>14</v>
-      </c>
-      <c r="F32" s="1" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="131.25">
@@ -1465,7 +1464,7 @@
         <v>14</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="37.5">
@@ -1473,19 +1472,19 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
+        <v>68</v>
+      </c>
+      <c r="C34">
+        <v>14</v>
+      </c>
+      <c r="D34" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="C34">
-        <v>14</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>70</v>
-      </c>
       <c r="E34">
         <v>14</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="37.5">
@@ -1493,19 +1492,19 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
+        <v>70</v>
+      </c>
+      <c r="C35">
+        <v>14</v>
+      </c>
+      <c r="D35" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="C35">
-        <v>14</v>
-      </c>
-      <c r="D35" s="1" t="s">
+      <c r="E35">
+        <v>14</v>
+      </c>
+      <c r="F35" s="1" t="s">
         <v>72</v>
-      </c>
-      <c r="E35">
-        <v>14</v>
-      </c>
-      <c r="F35" s="1" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="37.5">
@@ -1513,19 +1512,19 @@
         <v>34</v>
       </c>
       <c r="B36" t="s">
+        <v>73</v>
+      </c>
+      <c r="C36">
+        <v>14</v>
+      </c>
+      <c r="D36" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="C36">
-        <v>14</v>
-      </c>
-      <c r="D36" s="1" t="s">
-        <v>75</v>
-      </c>
       <c r="E36">
         <v>14</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="75">
@@ -1533,19 +1532,19 @@
         <v>35</v>
       </c>
       <c r="B37" t="s">
+        <v>76</v>
+      </c>
+      <c r="C37">
+        <v>14</v>
+      </c>
+      <c r="D37" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="C37">
-        <v>14</v>
-      </c>
-      <c r="D37" s="1" t="s">
-        <v>78</v>
-      </c>
       <c r="E37">
         <v>14</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="37.5">
@@ -1553,19 +1552,19 @@
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C38">
         <v>20</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E38">
         <v>16</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="39" spans="1:6">
@@ -1573,13 +1572,13 @@
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C39">
         <v>14</v>
       </c>
       <c r="D39" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E39">
         <v>14</v>
@@ -1590,13 +1589,13 @@
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C40">
         <v>14</v>
       </c>
       <c r="D40" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E40">
         <v>14</v>
@@ -1607,13 +1606,13 @@
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C41">
         <v>14</v>
       </c>
       <c r="D41" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E41">
         <v>14</v>
@@ -1624,7 +1623,7 @@
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C42">
         <v>20</v>
@@ -1636,7 +1635,7 @@
         <v>16</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="43" spans="1:6" ht="37.5">
@@ -1644,19 +1643,19 @@
         <v>41</v>
       </c>
       <c r="B43" t="s">
+        <v>87</v>
+      </c>
+      <c r="C43">
+        <v>14</v>
+      </c>
+      <c r="D43" t="s">
+        <v>89</v>
+      </c>
+      <c r="E43">
+        <v>14</v>
+      </c>
+      <c r="F43" s="1" t="s">
         <v>88</v>
-      </c>
-      <c r="C43">
-        <v>14</v>
-      </c>
-      <c r="D43" t="s">
-        <v>90</v>
-      </c>
-      <c r="E43">
-        <v>14</v>
-      </c>
-      <c r="F43" s="1" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="44" spans="1:6" ht="37.5">
@@ -1664,19 +1663,19 @@
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C44">
         <v>20</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E44">
         <v>20</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="45" spans="1:6" ht="37.5">
@@ -1684,13 +1683,13 @@
         <v>43</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C45">
         <v>12</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E45">
         <v>12</v>
@@ -1701,13 +1700,13 @@
         <v>44</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C46">
         <v>12</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E46">
         <v>12</v>

--- a/Assets/Originals/Excels/Button/ButtonMessage.xlsx
+++ b/Assets/Originals/Excels/Button/ButtonMessage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\Button\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F65EF84-C6F8-4249-8CAE-E7D527479504}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA1966B7-0971-4B4F-9F8E-EB1D906448CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="102">
   <si>
     <t>number</t>
     <phoneticPr fontId="1"/>
@@ -517,6 +517,27 @@
   </si>
   <si>
     <t>Compass description</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ExplanationPanel内の操作説明</t>
+    <rPh sb="16" eb="17">
+      <t>ナイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ExplanationPanel内のアイテム説明</t>
+    <rPh sb="16" eb="17">
+      <t>ナイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ExplanationPanel内のコンパス説明</t>
+    <rPh sb="16" eb="17">
+      <t>ナイ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -852,7 +873,7 @@
     <col min="3" max="3" width="20.5" customWidth="1"/>
     <col min="4" max="4" width="16.5" customWidth="1"/>
     <col min="5" max="5" width="18.625" customWidth="1"/>
-    <col min="6" max="6" width="12.375" style="1" customWidth="1"/>
+    <col min="6" max="6" width="24.375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -1125,7 +1146,7 @@
         <v>16</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>57</v>
+        <v>99</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="37.5">
@@ -1145,7 +1166,7 @@
         <v>16</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>57</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -1712,51 +1733,87 @@
         <v>12</v>
       </c>
     </row>
-    <row r="47" spans="1:6">
+    <row r="47" spans="1:6" ht="37.5">
       <c r="A47">
         <v>45</v>
       </c>
+      <c r="B47" t="s">
+        <v>29</v>
+      </c>
       <c r="C47">
-        <v>14</v>
+        <v>16</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>30</v>
       </c>
       <c r="E47">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6">
+        <v>16</v>
+      </c>
+      <c r="F47" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" ht="37.5">
       <c r="A48">
         <v>46</v>
       </c>
+      <c r="B48" t="s">
+        <v>31</v>
+      </c>
       <c r="C48">
-        <v>14</v>
+        <v>16</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="E48">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
+        <v>16</v>
+      </c>
+      <c r="F48" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" ht="37.5">
       <c r="A49">
         <v>47</v>
       </c>
+      <c r="B49" t="s">
+        <v>29</v>
+      </c>
       <c r="C49">
-        <v>14</v>
+        <v>16</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>30</v>
       </c>
       <c r="E49">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
+        <v>16</v>
+      </c>
+      <c r="F49" s="1" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" ht="37.5">
       <c r="A50">
         <v>48</v>
       </c>
+      <c r="B50" t="s">
+        <v>31</v>
+      </c>
       <c r="C50">
-        <v>14</v>
+        <v>16</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="E50">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
+        <v>16</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6">
       <c r="A51">
         <v>49</v>
       </c>
@@ -1767,7 +1824,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="52" spans="1:5">
+    <row r="52" spans="1:6">
       <c r="A52">
         <v>50</v>
       </c>
@@ -1778,7 +1835,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="53" spans="1:5">
+    <row r="53" spans="1:6">
       <c r="A53">
         <v>51</v>
       </c>
@@ -1789,7 +1846,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="54" spans="1:5">
+    <row r="54" spans="1:6">
       <c r="A54">
         <v>52</v>
       </c>
@@ -1800,7 +1857,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="55" spans="1:5">
+    <row r="55" spans="1:6">
       <c r="A55">
         <v>53</v>
       </c>
@@ -1811,7 +1868,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="56" spans="1:5">
+    <row r="56" spans="1:6">
       <c r="A56">
         <v>54</v>
       </c>
@@ -1822,7 +1879,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="57" spans="1:5">
+    <row r="57" spans="1:6">
       <c r="A57">
         <v>55</v>
       </c>
@@ -1833,7 +1890,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="58" spans="1:5">
+    <row r="58" spans="1:6">
       <c r="A58">
         <v>56</v>
       </c>
@@ -1844,7 +1901,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="59" spans="1:5">
+    <row r="59" spans="1:6">
       <c r="A59">
         <v>57</v>
       </c>
@@ -1855,7 +1912,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="60" spans="1:5">
+    <row r="60" spans="1:6">
       <c r="A60">
         <v>58</v>
       </c>
@@ -1866,7 +1923,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="61" spans="1:5">
+    <row r="61" spans="1:6">
       <c r="A61">
         <v>59</v>
       </c>
@@ -1877,7 +1934,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="62" spans="1:5">
+    <row r="62" spans="1:6">
       <c r="A62">
         <v>60</v>
       </c>
@@ -1888,7 +1945,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="63" spans="1:5">
+    <row r="63" spans="1:6">
       <c r="A63">
         <v>61</v>
       </c>
@@ -1899,7 +1956,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="64" spans="1:5">
+    <row r="64" spans="1:6">
       <c r="A64">
         <v>62</v>
       </c>

--- a/Assets/Originals/Excels/Button/ButtonMessage.xlsx
+++ b/Assets/Originals/Excels/Button/ButtonMessage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\Button\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA1966B7-0971-4B4F-9F8E-EB1D906448CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B43E4A66-47AB-4933-B9FE-CD860A725636}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -913,7 +913,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="75">
+    <row r="3" spans="1:6" ht="37.5">
       <c r="A3">
         <v>1</v>
       </c>
@@ -950,7 +950,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="56.25">
+    <row r="5" spans="1:6" ht="37.5">
       <c r="A5">
         <v>3</v>
       </c>
@@ -970,7 +970,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="37.5">
+    <row r="6" spans="1:6">
       <c r="A6">
         <v>4</v>
       </c>
@@ -1257,7 +1257,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="37.5">
+    <row r="22" spans="1:6">
       <c r="A22">
         <v>20</v>
       </c>
@@ -1348,7 +1348,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="27" spans="1:6" ht="75">
+    <row r="27" spans="1:6" ht="37.5">
       <c r="A27">
         <v>25</v>
       </c>
@@ -1368,7 +1368,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="28" spans="1:6" ht="75">
+    <row r="28" spans="1:6" ht="37.5">
       <c r="A28">
         <v>26</v>
       </c>
@@ -1388,7 +1388,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="29" spans="1:6" ht="37.5">
+    <row r="29" spans="1:6">
       <c r="A29">
         <v>27</v>
       </c>
@@ -1408,7 +1408,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="30" spans="1:6" ht="37.5">
+    <row r="30" spans="1:6">
       <c r="A30">
         <v>28</v>
       </c>
@@ -1428,7 +1428,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="31" spans="1:6" ht="56.25">
+    <row r="31" spans="1:6" ht="37.5">
       <c r="A31">
         <v>29</v>
       </c>
@@ -1448,7 +1448,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="32" spans="1:6" ht="37.5">
+    <row r="32" spans="1:6">
       <c r="A32">
         <v>30</v>
       </c>
@@ -1468,7 +1468,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="33" spans="1:6" ht="131.25">
+    <row r="33" spans="1:6" ht="75">
       <c r="A33">
         <v>31</v>
       </c>
@@ -1488,7 +1488,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="34" spans="1:6" ht="37.5">
+    <row r="34" spans="1:6">
       <c r="A34">
         <v>32</v>
       </c>
@@ -1508,7 +1508,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="35" spans="1:6" ht="37.5">
+    <row r="35" spans="1:6">
       <c r="A35">
         <v>33</v>
       </c>
@@ -1528,7 +1528,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="36" spans="1:6" ht="37.5">
+    <row r="36" spans="1:6">
       <c r="A36">
         <v>34</v>
       </c>
@@ -1548,7 +1548,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="37" spans="1:6" ht="75">
+    <row r="37" spans="1:6" ht="37.5">
       <c r="A37">
         <v>35</v>
       </c>
@@ -1639,7 +1639,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="42" spans="1:6" ht="56.25">
+    <row r="42" spans="1:6" ht="37.5">
       <c r="A42">
         <v>40</v>
       </c>
@@ -1659,7 +1659,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="43" spans="1:6" ht="37.5">
+    <row r="43" spans="1:6">
       <c r="A43">
         <v>41</v>
       </c>
@@ -1679,7 +1679,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="44" spans="1:6" ht="37.5">
+    <row r="44" spans="1:6">
       <c r="A44">
         <v>42</v>
       </c>
@@ -1707,13 +1707,13 @@
         <v>93</v>
       </c>
       <c r="C45">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D45" s="1" t="s">
         <v>92</v>
       </c>
       <c r="E45">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="46" spans="1:6" ht="37.5">
@@ -1724,13 +1724,13 @@
         <v>91</v>
       </c>
       <c r="C46">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D46" s="1" t="s">
         <v>94</v>
       </c>
       <c r="E46">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="47" spans="1:6" ht="37.5">

--- a/Assets/Originals/Excels/Button/ButtonMessage.xlsx
+++ b/Assets/Originals/Excels/Button/ButtonMessage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\Button\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B43E4A66-47AB-4933-B9FE-CD860A725636}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2B99512-6A31-48A8-9E16-670814D9C7D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="101">
   <si>
     <t>number</t>
     <phoneticPr fontId="1"/>
@@ -111,14 +111,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>明るさ(ゲーム開始後に設定することを推奨)</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Brightness (Recommended to adjust after starting the game)</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>画面モード</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -129,11 +121,6 @@
   </si>
   <si>
     <t>フルスクリーン</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t xml:space="preserve">
-Full screen</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -538,6 +525,14 @@
     <rPh sb="16" eb="17">
       <t>ナイ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Brightness </t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Full screen</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -893,7 +888,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -930,7 +925,7 @@
         <v>14</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -967,7 +962,7 @@
         <v>24</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -987,7 +982,7 @@
         <v>14</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -1024,18 +1019,18 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="75">
+    <row r="9" spans="1:6">
       <c r="A9">
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="C9">
         <v>12</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>18</v>
+        <v>99</v>
       </c>
       <c r="E9">
         <v>12</v>
@@ -1046,30 +1041,30 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C10">
         <v>10</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E10">
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="37.5">
+    <row r="11" spans="1:6">
       <c r="A11">
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C11">
         <v>16</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>22</v>
+        <v>100</v>
       </c>
       <c r="E11">
         <v>16</v>
@@ -1080,13 +1075,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C12">
         <v>16</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E12">
         <v>16</v>
@@ -1097,13 +1092,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C13">
         <v>10</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E13">
         <v>10</v>
@@ -1114,19 +1109,19 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C14">
         <v>10</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E14">
         <v>8</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="37.5">
@@ -1134,19 +1129,19 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C15">
         <v>16</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E15">
         <v>16</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="37.5">
@@ -1154,19 +1149,19 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C16">
         <v>16</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E16">
         <v>16</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -1174,13 +1169,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C17">
         <v>10</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="E17">
         <v>10</v>
@@ -1191,13 +1186,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C18">
         <v>10</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="E18">
         <v>8</v>
@@ -1208,13 +1203,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C19">
         <v>16</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E19">
         <v>16</v>
@@ -1225,13 +1220,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C20">
         <v>16</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E20">
         <v>16</v>
@@ -1242,7 +1237,7 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C21">
         <v>24</v>
@@ -1254,7 +1249,7 @@
         <v>18</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -1262,19 +1257,19 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C22">
         <v>24</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E22">
         <v>18</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -1282,19 +1277,19 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C23">
         <v>24</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="E23">
         <v>18</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -1302,13 +1297,13 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C24">
         <v>24</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="E24">
         <v>18</v>
@@ -1319,13 +1314,13 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C25">
         <v>24</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E25">
         <v>18</v>
@@ -1336,13 +1331,13 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="C26">
         <v>24</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E26">
         <v>18</v>
@@ -1353,19 +1348,19 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C27">
         <v>32</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="E27">
         <v>32</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="37.5">
@@ -1373,19 +1368,19 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C28">
         <v>32</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="E28">
         <v>32</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="29" spans="1:6">
@@ -1393,19 +1388,19 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C29">
         <v>14</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="E29">
         <v>14</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="30" spans="1:6">
@@ -1413,19 +1408,19 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C30">
         <v>14</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="E30">
         <v>14</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="37.5">
@@ -1433,19 +1428,19 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C31">
         <v>12</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="E31">
         <v>12</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="32" spans="1:6">
@@ -1453,19 +1448,19 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C32">
         <v>14</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="E32">
         <v>14</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="75">
@@ -1485,7 +1480,7 @@
         <v>14</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="34" spans="1:6">
@@ -1493,19 +1488,19 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C34">
         <v>14</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="E34">
         <v>14</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
     </row>
     <row r="35" spans="1:6">
@@ -1513,19 +1508,19 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C35">
         <v>14</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="E35">
         <v>14</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="36" spans="1:6">
@@ -1533,19 +1528,19 @@
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C36">
         <v>14</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="E36">
         <v>14</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="37.5">
@@ -1553,19 +1548,19 @@
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C37">
         <v>14</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="E37">
         <v>14</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="37.5">
@@ -1573,19 +1568,19 @@
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C38">
         <v>20</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="E38">
         <v>16</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
     </row>
     <row r="39" spans="1:6">
@@ -1593,13 +1588,13 @@
         <v>37</v>
       </c>
       <c r="B39" t="s">
+        <v>76</v>
+      </c>
+      <c r="C39">
+        <v>14</v>
+      </c>
+      <c r="D39" t="s">
         <v>79</v>
-      </c>
-      <c r="C39">
-        <v>14</v>
-      </c>
-      <c r="D39" t="s">
-        <v>82</v>
       </c>
       <c r="E39">
         <v>14</v>
@@ -1610,13 +1605,13 @@
         <v>38</v>
       </c>
       <c r="B40" t="s">
+        <v>77</v>
+      </c>
+      <c r="C40">
+        <v>14</v>
+      </c>
+      <c r="D40" t="s">
         <v>80</v>
-      </c>
-      <c r="C40">
-        <v>14</v>
-      </c>
-      <c r="D40" t="s">
-        <v>83</v>
       </c>
       <c r="E40">
         <v>14</v>
@@ -1627,13 +1622,13 @@
         <v>39</v>
       </c>
       <c r="B41" t="s">
+        <v>78</v>
+      </c>
+      <c r="C41">
+        <v>14</v>
+      </c>
+      <c r="D41" t="s">
         <v>81</v>
-      </c>
-      <c r="C41">
-        <v>14</v>
-      </c>
-      <c r="D41" t="s">
-        <v>84</v>
       </c>
       <c r="E41">
         <v>14</v>
@@ -1644,7 +1639,7 @@
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C42">
         <v>20</v>
@@ -1656,7 +1651,7 @@
         <v>16</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
     </row>
     <row r="43" spans="1:6">
@@ -1664,19 +1659,19 @@
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C43">
         <v>14</v>
       </c>
       <c r="D43" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="E43">
         <v>14</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
     </row>
     <row r="44" spans="1:6">
@@ -1684,19 +1679,19 @@
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C44">
         <v>20</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="E44">
         <v>20</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
     <row r="45" spans="1:6" ht="37.5">
@@ -1704,13 +1699,13 @@
         <v>43</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C45">
         <v>10</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="E45">
         <v>10</v>
@@ -1721,13 +1716,13 @@
         <v>44</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C46">
         <v>10</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="E46">
         <v>10</v>
@@ -1738,19 +1733,19 @@
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C47">
         <v>16</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E47">
         <v>16</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
     </row>
     <row r="48" spans="1:6" ht="37.5">
@@ -1758,19 +1753,19 @@
         <v>46</v>
       </c>
       <c r="B48" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C48">
         <v>16</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E48">
         <v>16</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
     </row>
     <row r="49" spans="1:6" ht="37.5">
@@ -1778,19 +1773,19 @@
         <v>47</v>
       </c>
       <c r="B49" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C49">
         <v>16</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E49">
         <v>16</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="50" spans="1:6" ht="37.5">
@@ -1798,19 +1793,19 @@
         <v>48</v>
       </c>
       <c r="B50" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C50">
         <v>16</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E50">
         <v>16</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="51" spans="1:6">

--- a/Assets/Originals/Excels/Button/ButtonMessage.xlsx
+++ b/Assets/Originals/Excels/Button/ButtonMessage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\Button\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2B99512-6A31-48A8-9E16-670814D9C7D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64557B11-15D8-4C79-902C-A8437B02C507}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -356,10 +356,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>MysteryItem</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>続ける</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -379,10 +375,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>Item confirmation</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>タイトル画面・PausePanel内</t>
     <rPh sb="4" eb="6">
       <t>ガメン</t>
@@ -533,6 +525,14 @@
   </si>
   <si>
     <t>Full screen</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Item check</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Mystery Item</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -925,7 +925,7 @@
         <v>14</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -1030,7 +1030,7 @@
         <v>12</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E9">
         <v>12</v>
@@ -1064,7 +1064,7 @@
         <v>16</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E11">
         <v>16</v>
@@ -1141,7 +1141,7 @@
         <v>16</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="37.5">
@@ -1161,7 +1161,7 @@
         <v>16</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -1192,7 +1192,7 @@
         <v>10</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E18">
         <v>8</v>
@@ -1480,7 +1480,7 @@
         <v>14</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="34" spans="1:6">
@@ -1494,7 +1494,7 @@
         <v>14</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>66</v>
+        <v>100</v>
       </c>
       <c r="E34">
         <v>14</v>
@@ -1508,19 +1508,19 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
+        <v>66</v>
+      </c>
+      <c r="C35">
+        <v>14</v>
+      </c>
+      <c r="D35" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="C35">
-        <v>14</v>
-      </c>
-      <c r="D35" s="1" t="s">
+      <c r="E35">
+        <v>14</v>
+      </c>
+      <c r="F35" s="1" t="s">
         <v>68</v>
-      </c>
-      <c r="E35">
-        <v>14</v>
-      </c>
-      <c r="F35" s="1" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="36" spans="1:6">
@@ -1528,19 +1528,19 @@
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C36">
         <v>14</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>71</v>
+        <v>99</v>
       </c>
       <c r="E36">
         <v>14</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="37.5">
@@ -1548,19 +1548,19 @@
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C37">
         <v>14</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E37">
         <v>14</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="37.5">
@@ -1568,19 +1568,19 @@
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C38">
         <v>20</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E38">
         <v>16</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="39" spans="1:6">
@@ -1588,13 +1588,13 @@
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C39">
         <v>14</v>
       </c>
       <c r="D39" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E39">
         <v>14</v>
@@ -1605,13 +1605,13 @@
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C40">
         <v>14</v>
       </c>
       <c r="D40" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E40">
         <v>14</v>
@@ -1622,13 +1622,13 @@
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C41">
         <v>14</v>
       </c>
       <c r="D41" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E41">
         <v>14</v>
@@ -1651,7 +1651,7 @@
         <v>16</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="43" spans="1:6">
@@ -1659,19 +1659,19 @@
         <v>41</v>
       </c>
       <c r="B43" t="s">
+        <v>82</v>
+      </c>
+      <c r="C43">
+        <v>14</v>
+      </c>
+      <c r="D43" t="s">
         <v>84</v>
       </c>
-      <c r="C43">
-        <v>14</v>
-      </c>
-      <c r="D43" t="s">
-        <v>86</v>
-      </c>
       <c r="E43">
         <v>14</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="44" spans="1:6">
@@ -1679,19 +1679,19 @@
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C44">
         <v>20</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E44">
         <v>20</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="45" spans="1:6" ht="37.5">
@@ -1699,13 +1699,13 @@
         <v>43</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C45">
         <v>10</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E45">
         <v>10</v>
@@ -1716,13 +1716,13 @@
         <v>44</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C46">
         <v>10</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E46">
         <v>10</v>
@@ -1745,7 +1745,7 @@
         <v>16</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="48" spans="1:6" ht="37.5">
@@ -1765,7 +1765,7 @@
         <v>16</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="49" spans="1:6" ht="37.5">
@@ -1785,7 +1785,7 @@
         <v>16</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="50" spans="1:6" ht="37.5">
@@ -1805,7 +1805,7 @@
         <v>16</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="51" spans="1:6">

--- a/Assets/Originals/Excels/Button/ButtonMessage.xlsx
+++ b/Assets/Originals/Excels/Button/ButtonMessage.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\Button\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64557B11-15D8-4C79-902C-A8437B02C507}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3678B814-C79D-4B26-8E14-622C8EA09649}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="140">
   <si>
     <t>number</t>
     <phoneticPr fontId="1"/>
@@ -533,6 +533,128 @@
   </si>
   <si>
     <t>Mystery Item</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>开始游戏</t>
+  </si>
+  <si>
+    <t>选项</t>
+  </si>
+  <si>
+    <t>结束游戏</t>
+  </si>
+  <si>
+    <t>返回</t>
+  </si>
+  <si>
+    <t>灵敏度</t>
+  </si>
+  <si>
+    <t>BGM</t>
+  </si>
+  <si>
+    <t>亮度</t>
+  </si>
+  <si>
+    <t>画面模式</t>
+  </si>
+  <si>
+    <t>全屏</t>
+  </si>
+  <si>
+    <t>窗口</t>
+  </si>
+  <si>
+    <t>分辨率</t>
+  </si>
+  <si>
+    <t>操作说明</t>
+  </si>
+  <si>
+    <t>显示</t>
+  </si>
+  <si>
+    <t>隐藏</t>
+  </si>
+  <si>
+    <t>物品说明</t>
+  </si>
+  <si>
+    <t>罗盘说明</t>
+  </si>
+  <si>
+    <t>日本語</t>
+  </si>
+  <si>
+    <t>English</t>
+  </si>
+  <si>
+    <t>音量调整</t>
+  </si>
+  <si>
+    <t>画面</t>
+  </si>
+  <si>
+    <t>说明</t>
+  </si>
+  <si>
+    <t>语言</t>
+  </si>
+  <si>
+    <t>是</t>
+  </si>
+  <si>
+    <t>否</t>
+  </si>
+  <si>
+    <t>文件</t>
+  </si>
+  <si>
+    <t>神秘物品</t>
+  </si>
+  <si>
+    <t>继续</t>
+  </si>
+  <si>
+    <t>物品确认</t>
+  </si>
+  <si>
+    <t>返回标题</t>
+  </si>
+  <si>
+    <t>幽狱迷宫</t>
+  </si>
+  <si>
+    <t>梦想</t>
+  </si>
+  <si>
+    <t>梦幻</t>
+  </si>
+  <si>
+    <t>噩梦</t>
+  </si>
+  <si>
+    <t>重新开始</t>
+  </si>
+  <si>
+    <t>问卷调查
+请点击这里！</t>
+  </si>
+  <si>
+    <t>愿望单
+请点击这里！</t>
+  </si>
+  <si>
+    <t>messageChinese01</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>messageSizeChinese01</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>簡体中国語</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -540,7 +662,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -554,6 +676,18 @@
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Microsoft YaHei"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
     </font>
   </fonts>
   <fills count="2">
@@ -576,11 +710,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -861,17 +1000,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F102"/>
+  <dimension ref="A1:H102"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="2" max="2" width="51.25" customWidth="1"/>
     <col min="3" max="3" width="20.5" customWidth="1"/>
     <col min="4" max="4" width="16.5" customWidth="1"/>
     <col min="5" max="5" width="18.625" customWidth="1"/>
-    <col min="6" max="6" width="24.375" style="1" customWidth="1"/>
+    <col min="6" max="6" width="20.25" customWidth="1"/>
+    <col min="7" max="7" width="24.875" customWidth="1"/>
+    <col min="8" max="8" width="24.375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:8">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -887,11 +1028,17 @@
       <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
+        <v>137</v>
+      </c>
+      <c r="G1" t="s">
+        <v>138</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:8">
       <c r="A2">
         <v>0</v>
       </c>
@@ -907,8 +1054,14 @@
       <c r="E2">
         <v>14</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" ht="37.5">
+      <c r="F2" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="G2" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="37.5">
       <c r="A3">
         <v>1</v>
       </c>
@@ -924,11 +1077,17 @@
       <c r="E3">
         <v>14</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="G3" s="2">
+        <v>14</v>
+      </c>
+      <c r="H3" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:8">
       <c r="A4">
         <v>2</v>
       </c>
@@ -944,8 +1103,14 @@
       <c r="E4">
         <v>14</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" ht="37.5">
+      <c r="F4" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="G4" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="37.5">
       <c r="A5">
         <v>3</v>
       </c>
@@ -961,11 +1126,17 @@
       <c r="E5">
         <v>24</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="F5" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="G5" s="2">
+        <v>24</v>
+      </c>
+      <c r="H5" s="1" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:8">
       <c r="A6">
         <v>4</v>
       </c>
@@ -981,11 +1152,17 @@
       <c r="E6">
         <v>14</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="F6" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="G6" s="2">
+        <v>14</v>
+      </c>
+      <c r="H6" s="1" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:8">
       <c r="A7">
         <v>5</v>
       </c>
@@ -1001,8 +1178,14 @@
       <c r="E7">
         <v>14</v>
       </c>
-    </row>
-    <row r="8" spans="1:6">
+      <c r="F7" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="G7" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
       <c r="A8">
         <v>6</v>
       </c>
@@ -1018,8 +1201,14 @@
       <c r="E8">
         <v>14</v>
       </c>
-    </row>
-    <row r="9" spans="1:6">
+      <c r="F8" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G8" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
       <c r="A9">
         <v>7</v>
       </c>
@@ -1035,8 +1224,14 @@
       <c r="E9">
         <v>12</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" ht="37.5">
+      <c r="F9" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="G9" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="37.5">
       <c r="A10">
         <v>8</v>
       </c>
@@ -1052,8 +1247,14 @@
       <c r="E10">
         <v>10</v>
       </c>
-    </row>
-    <row r="11" spans="1:6">
+      <c r="F10" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="G10" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
       <c r="A11">
         <v>9</v>
       </c>
@@ -1069,8 +1270,14 @@
       <c r="E11">
         <v>16</v>
       </c>
-    </row>
-    <row r="12" spans="1:6">
+      <c r="F11" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="G11" s="2">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
       <c r="A12">
         <v>10</v>
       </c>
@@ -1086,8 +1293,14 @@
       <c r="E12">
         <v>16</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" ht="37.5">
+      <c r="F12" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="G12" s="2">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="37.5">
       <c r="A13">
         <v>11</v>
       </c>
@@ -1103,8 +1316,14 @@
       <c r="E13">
         <v>10</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" ht="37.5">
+      <c r="F13" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="G13" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="37.5">
       <c r="A14">
         <v>12</v>
       </c>
@@ -1120,11 +1339,17 @@
       <c r="E14">
         <v>8</v>
       </c>
-      <c r="F14" s="1" t="s">
+      <c r="F14" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="G14" s="2">
+        <v>10</v>
+      </c>
+      <c r="H14" s="1" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="37.5">
+    <row r="15" spans="1:8" ht="37.5">
       <c r="A15">
         <v>13</v>
       </c>
@@ -1140,11 +1365,17 @@
       <c r="E15">
         <v>16</v>
       </c>
-      <c r="F15" s="1" t="s">
+      <c r="F15" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="G15" s="2">
+        <v>16</v>
+      </c>
+      <c r="H15" s="1" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="37.5">
+    <row r="16" spans="1:8" ht="37.5">
       <c r="A16">
         <v>14</v>
       </c>
@@ -1160,11 +1391,17 @@
       <c r="E16">
         <v>16</v>
       </c>
-      <c r="F16" s="1" t="s">
+      <c r="F16" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="G16" s="2">
+        <v>16</v>
+      </c>
+      <c r="H16" s="1" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="17" spans="1:6">
+    <row r="17" spans="1:8">
       <c r="A17">
         <v>15</v>
       </c>
@@ -1180,8 +1417,14 @@
       <c r="E17">
         <v>10</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" ht="37.5">
+      <c r="F17" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="G17" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="37.5">
       <c r="A18">
         <v>16</v>
       </c>
@@ -1197,8 +1440,14 @@
       <c r="E18">
         <v>8</v>
       </c>
-    </row>
-    <row r="19" spans="1:6">
+      <c r="F18" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="G18" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
       <c r="A19">
         <v>17</v>
       </c>
@@ -1214,8 +1463,14 @@
       <c r="E19">
         <v>16</v>
       </c>
-    </row>
-    <row r="20" spans="1:6">
+      <c r="F19" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="G19" s="2">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
       <c r="A20">
         <v>18</v>
       </c>
@@ -1231,8 +1486,14 @@
       <c r="E20">
         <v>16</v>
       </c>
-    </row>
-    <row r="21" spans="1:6">
+      <c r="F20" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="G20" s="2">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
       <c r="A21">
         <v>19</v>
       </c>
@@ -1248,11 +1509,17 @@
       <c r="E21">
         <v>18</v>
       </c>
-      <c r="F21" s="1" t="s">
+      <c r="F21" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="G21" s="2">
+        <v>24</v>
+      </c>
+      <c r="H21" s="1" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="22" spans="1:6">
+    <row r="22" spans="1:8">
       <c r="A22">
         <v>20</v>
       </c>
@@ -1268,11 +1535,17 @@
       <c r="E22">
         <v>18</v>
       </c>
-      <c r="F22" s="1" t="s">
+      <c r="F22" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="G22" s="2">
+        <v>24</v>
+      </c>
+      <c r="H22" s="1" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="23" spans="1:6">
+    <row r="23" spans="1:8">
       <c r="A23">
         <v>21</v>
       </c>
@@ -1288,11 +1561,17 @@
       <c r="E23">
         <v>18</v>
       </c>
-      <c r="F23" s="1" t="s">
+      <c r="F23" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="G23" s="2">
+        <v>24</v>
+      </c>
+      <c r="H23" s="1" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="24" spans="1:6">
+    <row r="24" spans="1:8">
       <c r="A24">
         <v>22</v>
       </c>
@@ -1308,8 +1587,14 @@
       <c r="E24">
         <v>18</v>
       </c>
-    </row>
-    <row r="25" spans="1:6">
+      <c r="F24" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="G24" s="2">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
       <c r="A25">
         <v>23</v>
       </c>
@@ -1325,8 +1610,14 @@
       <c r="E25">
         <v>18</v>
       </c>
-    </row>
-    <row r="26" spans="1:6">
+      <c r="F25" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="G25" s="2">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
       <c r="A26">
         <v>24</v>
       </c>
@@ -1342,8 +1633,14 @@
       <c r="E26">
         <v>18</v>
       </c>
-    </row>
-    <row r="27" spans="1:6" ht="37.5">
+      <c r="F26" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="G26" s="2">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" ht="37.5">
       <c r="A27">
         <v>25</v>
       </c>
@@ -1359,11 +1656,17 @@
       <c r="E27">
         <v>32</v>
       </c>
-      <c r="F27" s="1" t="s">
+      <c r="F27" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="G27" s="2">
+        <v>32</v>
+      </c>
+      <c r="H27" s="1" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="28" spans="1:6" ht="37.5">
+    <row r="28" spans="1:8" ht="37.5">
       <c r="A28">
         <v>26</v>
       </c>
@@ -1379,11 +1682,17 @@
       <c r="E28">
         <v>32</v>
       </c>
-      <c r="F28" s="1" t="s">
+      <c r="F28" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="G28" s="2">
+        <v>32</v>
+      </c>
+      <c r="H28" s="1" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="29" spans="1:6">
+    <row r="29" spans="1:8">
       <c r="A29">
         <v>27</v>
       </c>
@@ -1399,11 +1708,17 @@
       <c r="E29">
         <v>14</v>
       </c>
-      <c r="F29" s="1" t="s">
+      <c r="F29" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="G29" s="2">
+        <v>14</v>
+      </c>
+      <c r="H29" s="1" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="30" spans="1:6">
+    <row r="30" spans="1:8">
       <c r="A30">
         <v>28</v>
       </c>
@@ -1419,11 +1734,17 @@
       <c r="E30">
         <v>14</v>
       </c>
-      <c r="F30" s="1" t="s">
+      <c r="F30" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="G30" s="2">
+        <v>14</v>
+      </c>
+      <c r="H30" s="1" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="31" spans="1:6" ht="37.5">
+    <row r="31" spans="1:8" ht="37.5">
       <c r="A31">
         <v>29</v>
       </c>
@@ -1439,11 +1760,17 @@
       <c r="E31">
         <v>12</v>
       </c>
-      <c r="F31" s="1" t="s">
+      <c r="F31" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="G31" s="2">
+        <v>12</v>
+      </c>
+      <c r="H31" s="1" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="32" spans="1:6">
+    <row r="32" spans="1:8">
       <c r="A32">
         <v>30</v>
       </c>
@@ -1459,11 +1786,17 @@
       <c r="E32">
         <v>14</v>
       </c>
-      <c r="F32" s="1" t="s">
+      <c r="F32" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="G32" s="2">
+        <v>14</v>
+      </c>
+      <c r="H32" s="1" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="33" spans="1:6" ht="75">
+    <row r="33" spans="1:8" ht="75">
       <c r="A33">
         <v>31</v>
       </c>
@@ -1479,11 +1812,17 @@
       <c r="E33">
         <v>14</v>
       </c>
-      <c r="F33" s="1" t="s">
+      <c r="F33" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="G33" s="2">
+        <v>14</v>
+      </c>
+      <c r="H33" s="1" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="34" spans="1:6">
+    <row r="34" spans="1:8">
       <c r="A34">
         <v>32</v>
       </c>
@@ -1499,11 +1838,17 @@
       <c r="E34">
         <v>14</v>
       </c>
-      <c r="F34" s="1" t="s">
+      <c r="F34" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="G34" s="2">
+        <v>14</v>
+      </c>
+      <c r="H34" s="1" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="35" spans="1:6">
+    <row r="35" spans="1:8">
       <c r="A35">
         <v>33</v>
       </c>
@@ -1519,11 +1864,17 @@
       <c r="E35">
         <v>14</v>
       </c>
-      <c r="F35" s="1" t="s">
+      <c r="F35" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="G35" s="2">
+        <v>14</v>
+      </c>
+      <c r="H35" s="1" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="36" spans="1:6">
+    <row r="36" spans="1:8">
       <c r="A36">
         <v>34</v>
       </c>
@@ -1539,11 +1890,17 @@
       <c r="E36">
         <v>14</v>
       </c>
-      <c r="F36" s="1" t="s">
+      <c r="F36" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="G36" s="2">
+        <v>14</v>
+      </c>
+      <c r="H36" s="1" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="37" spans="1:6" ht="37.5">
+    <row r="37" spans="1:8" ht="37.5">
       <c r="A37">
         <v>35</v>
       </c>
@@ -1559,11 +1916,17 @@
       <c r="E37">
         <v>14</v>
       </c>
-      <c r="F37" s="1" t="s">
+      <c r="F37" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="G37" s="2">
+        <v>14</v>
+      </c>
+      <c r="H37" s="1" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="38" spans="1:6" ht="37.5">
+    <row r="38" spans="1:8" ht="37.5">
       <c r="A38">
         <v>36</v>
       </c>
@@ -1579,11 +1942,17 @@
       <c r="E38">
         <v>16</v>
       </c>
-      <c r="F38" s="1" t="s">
+      <c r="F38" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="G38" s="2">
+        <v>20</v>
+      </c>
+      <c r="H38" s="1" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="39" spans="1:6">
+    <row r="39" spans="1:8">
       <c r="A39">
         <v>37</v>
       </c>
@@ -1599,8 +1968,14 @@
       <c r="E39">
         <v>14</v>
       </c>
-    </row>
-    <row r="40" spans="1:6">
+      <c r="F39" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="G39" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8">
       <c r="A40">
         <v>38</v>
       </c>
@@ -1616,8 +1991,14 @@
       <c r="E40">
         <v>14</v>
       </c>
-    </row>
-    <row r="41" spans="1:6">
+      <c r="F40" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="G40" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8">
       <c r="A41">
         <v>39</v>
       </c>
@@ -1633,8 +2014,14 @@
       <c r="E41">
         <v>14</v>
       </c>
-    </row>
-    <row r="42" spans="1:6" ht="37.5">
+      <c r="F41" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="G41" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" ht="37.5">
       <c r="A42">
         <v>40</v>
       </c>
@@ -1650,11 +2037,17 @@
       <c r="E42">
         <v>16</v>
       </c>
-      <c r="F42" s="1" t="s">
+      <c r="F42" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="G42" s="2">
+        <v>20</v>
+      </c>
+      <c r="H42" s="1" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="43" spans="1:6">
+    <row r="43" spans="1:8">
       <c r="A43">
         <v>41</v>
       </c>
@@ -1670,11 +2063,17 @@
       <c r="E43">
         <v>14</v>
       </c>
-      <c r="F43" s="1" t="s">
+      <c r="F43" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="G43" s="2">
+        <v>14</v>
+      </c>
+      <c r="H43" s="1" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="44" spans="1:6">
+    <row r="44" spans="1:8">
       <c r="A44">
         <v>42</v>
       </c>
@@ -1690,11 +2089,17 @@
       <c r="E44">
         <v>20</v>
       </c>
-      <c r="F44" s="1" t="s">
+      <c r="F44" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="G44" s="2">
+        <v>20</v>
+      </c>
+      <c r="H44" s="1" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="45" spans="1:6" ht="37.5">
+    <row r="45" spans="1:8" ht="51">
       <c r="A45">
         <v>43</v>
       </c>
@@ -1710,8 +2115,14 @@
       <c r="E45">
         <v>10</v>
       </c>
-    </row>
-    <row r="46" spans="1:6" ht="37.5">
+      <c r="F45" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="G45" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" ht="51">
       <c r="A46">
         <v>44</v>
       </c>
@@ -1727,8 +2138,14 @@
       <c r="E46">
         <v>10</v>
       </c>
-    </row>
-    <row r="47" spans="1:6" ht="37.5">
+      <c r="F46" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="G46" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" ht="37.5">
       <c r="A47">
         <v>45</v>
       </c>
@@ -1744,11 +2161,17 @@
       <c r="E47">
         <v>16</v>
       </c>
-      <c r="F47" s="1" t="s">
+      <c r="F47" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="G47" s="2">
+        <v>16</v>
+      </c>
+      <c r="H47" s="1" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="48" spans="1:6" ht="37.5">
+    <row r="48" spans="1:8" ht="37.5">
       <c r="A48">
         <v>46</v>
       </c>
@@ -1764,11 +2187,17 @@
       <c r="E48">
         <v>16</v>
       </c>
-      <c r="F48" s="1" t="s">
+      <c r="F48" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="G48" s="2">
+        <v>16</v>
+      </c>
+      <c r="H48" s="1" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="49" spans="1:6" ht="37.5">
+    <row r="49" spans="1:8" ht="37.5">
       <c r="A49">
         <v>47</v>
       </c>
@@ -1784,11 +2213,17 @@
       <c r="E49">
         <v>16</v>
       </c>
-      <c r="F49" s="1" t="s">
+      <c r="F49" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="G49" s="2">
+        <v>16</v>
+      </c>
+      <c r="H49" s="1" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="50" spans="1:6" ht="37.5">
+    <row r="50" spans="1:8" ht="37.5">
       <c r="A50">
         <v>48</v>
       </c>
@@ -1804,22 +2239,40 @@
       <c r="E50">
         <v>16</v>
       </c>
-      <c r="F50" s="1" t="s">
+      <c r="F50" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="G50" s="2">
+        <v>16</v>
+      </c>
+      <c r="H50" s="1" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="51" spans="1:6">
+    <row r="51" spans="1:8">
       <c r="A51">
         <v>49</v>
       </c>
+      <c r="B51" t="s">
+        <v>139</v>
+      </c>
       <c r="C51">
-        <v>14</v>
+        <v>10</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>139</v>
       </c>
       <c r="E51">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6">
+        <v>10</v>
+      </c>
+      <c r="F51" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="G51" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8">
       <c r="A52">
         <v>50</v>
       </c>
@@ -1830,7 +2283,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="53" spans="1:6">
+    <row r="53" spans="1:8">
       <c r="A53">
         <v>51</v>
       </c>
@@ -1841,7 +2294,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="54" spans="1:6">
+    <row r="54" spans="1:8">
       <c r="A54">
         <v>52</v>
       </c>
@@ -1852,7 +2305,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="55" spans="1:6">
+    <row r="55" spans="1:8">
       <c r="A55">
         <v>53</v>
       </c>
@@ -1863,7 +2316,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="56" spans="1:6">
+    <row r="56" spans="1:8">
       <c r="A56">
         <v>54</v>
       </c>
@@ -1874,7 +2327,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="57" spans="1:6">
+    <row r="57" spans="1:8">
       <c r="A57">
         <v>55</v>
       </c>
@@ -1885,7 +2338,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="58" spans="1:6">
+    <row r="58" spans="1:8">
       <c r="A58">
         <v>56</v>
       </c>
@@ -1896,7 +2349,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="59" spans="1:6">
+    <row r="59" spans="1:8">
       <c r="A59">
         <v>57</v>
       </c>
@@ -1907,7 +2360,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="60" spans="1:6">
+    <row r="60" spans="1:8">
       <c r="A60">
         <v>58</v>
       </c>
@@ -1918,7 +2371,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="61" spans="1:6">
+    <row r="61" spans="1:8">
       <c r="A61">
         <v>59</v>
       </c>
@@ -1929,7 +2382,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="62" spans="1:6">
+    <row r="62" spans="1:8">
       <c r="A62">
         <v>60</v>
       </c>
@@ -1940,7 +2393,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="63" spans="1:6">
+    <row r="63" spans="1:8">
       <c r="A63">
         <v>61</v>
       </c>
@@ -1951,7 +2404,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="64" spans="1:6">
+    <row r="64" spans="1:8">
       <c r="A64">
         <v>62</v>
       </c>

--- a/Assets/Originals/Excels/Button/ButtonMessage.xlsx
+++ b/Assets/Originals/Excels/Button/ButtonMessage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\Button\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3678B814-C79D-4B26-8E14-622C8EA09649}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52D1FD82-60B0-4D0F-AD8B-75F9EA2B5F5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="172">
   <si>
     <t>number</t>
     <phoneticPr fontId="1"/>
@@ -657,12 +657,133 @@
     <t>簡体中国語</t>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <t>開始遊戲</t>
+  </si>
+  <si>
+    <t>選項</t>
+  </si>
+  <si>
+    <t>結束遊戲</t>
+  </si>
+  <si>
+    <t>靈敏度</t>
+  </si>
+  <si>
+    <t>音效</t>
+  </si>
+  <si>
+    <t>畫面模式</t>
+  </si>
+  <si>
+    <t>視窗</t>
+  </si>
+  <si>
+    <t>解析度</t>
+  </si>
+  <si>
+    <t>操作說明</t>
+  </si>
+  <si>
+    <t>顯示</t>
+  </si>
+  <si>
+    <t>隱藏</t>
+  </si>
+  <si>
+    <t>物品說明</t>
+  </si>
+  <si>
+    <t>羅盤說明</t>
+  </si>
+  <si>
+    <t>音量調整</t>
+  </si>
+  <si>
+    <t>畫面</t>
+  </si>
+  <si>
+    <t>說明</t>
+  </si>
+  <si>
+    <t>語言</t>
+  </si>
+  <si>
+    <t>檔案</t>
+  </si>
+  <si>
+    <t>繼續</t>
+  </si>
+  <si>
+    <t>物品確認</t>
+  </si>
+  <si>
+    <t>返回標題</t>
+  </si>
+  <si>
+    <t>幽獄迷宮</t>
+  </si>
+  <si>
+    <t>夢想</t>
+  </si>
+  <si>
+    <t>夢幻</t>
+  </si>
+  <si>
+    <t>噩夢</t>
+  </si>
+  <si>
+    <t>重新開始</t>
+  </si>
+  <si>
+    <t>問卷調查
+請點選這裡！</t>
+  </si>
+  <si>
+    <t>願望單
+請點選這裡！</t>
+  </si>
+  <si>
+    <t>messageChinese02</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>messageSizeChinese02</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>繁体中国語</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <t>繁体中</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+      </rPr>
+      <t>国</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>語</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -689,6 +810,17 @@
       <family val="2"/>
       <charset val="128"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Microsoft JhengHei"/>
+      <family val="2"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Yu Gothic"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -710,7 +842,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -720,6 +852,10 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -1000,7 +1136,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H102"/>
+  <dimension ref="A1:J102"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="2" max="2" width="51.25" customWidth="1"/>
@@ -1009,10 +1145,12 @@
     <col min="5" max="5" width="18.625" customWidth="1"/>
     <col min="6" max="6" width="20.25" customWidth="1"/>
     <col min="7" max="7" width="24.875" customWidth="1"/>
-    <col min="8" max="8" width="24.375" style="1" customWidth="1"/>
+    <col min="8" max="8" width="22.25" customWidth="1"/>
+    <col min="9" max="9" width="22.5" customWidth="1"/>
+    <col min="10" max="10" width="24.375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:10">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1034,11 +1172,17 @@
       <c r="G1" t="s">
         <v>138</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
+        <v>168</v>
+      </c>
+      <c r="I1" t="s">
+        <v>169</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:10">
       <c r="A2">
         <v>0</v>
       </c>
@@ -1060,8 +1204,14 @@
       <c r="G2" s="2">
         <v>14</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" ht="37.5">
+      <c r="H2" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="I2" s="5">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="37.5">
       <c r="A3">
         <v>1</v>
       </c>
@@ -1083,11 +1233,17 @@
       <c r="G3" s="2">
         <v>14</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="H3" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="I3" s="5">
+        <v>14</v>
+      </c>
+      <c r="J3" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:10">
       <c r="A4">
         <v>2</v>
       </c>
@@ -1109,8 +1265,14 @@
       <c r="G4" s="2">
         <v>14</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" ht="37.5">
+      <c r="H4" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="I4" s="5">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="37.5">
       <c r="A5">
         <v>3</v>
       </c>
@@ -1132,11 +1294,17 @@
       <c r="G5" s="2">
         <v>24</v>
       </c>
-      <c r="H5" s="1" t="s">
+      <c r="H5" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="I5" s="5">
+        <v>24</v>
+      </c>
+      <c r="J5" s="1" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:10">
       <c r="A6">
         <v>4</v>
       </c>
@@ -1158,11 +1326,17 @@
       <c r="G6" s="2">
         <v>14</v>
       </c>
-      <c r="H6" s="1" t="s">
+      <c r="H6" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="I6" s="5">
+        <v>14</v>
+      </c>
+      <c r="J6" s="1" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:10">
       <c r="A7">
         <v>5</v>
       </c>
@@ -1184,8 +1358,14 @@
       <c r="G7" s="2">
         <v>14</v>
       </c>
-    </row>
-    <row r="8" spans="1:8">
+      <c r="H7" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="I7" s="5">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
       <c r="A8">
         <v>6</v>
       </c>
@@ -1207,8 +1387,14 @@
       <c r="G8" s="2">
         <v>14</v>
       </c>
-    </row>
-    <row r="9" spans="1:8">
+      <c r="H8" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="I8" s="5">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
       <c r="A9">
         <v>7</v>
       </c>
@@ -1230,8 +1416,14 @@
       <c r="G9" s="2">
         <v>12</v>
       </c>
-    </row>
-    <row r="10" spans="1:8" ht="37.5">
+      <c r="H9" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="I9" s="5">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="37.5">
       <c r="A10">
         <v>8</v>
       </c>
@@ -1253,8 +1445,14 @@
       <c r="G10" s="2">
         <v>10</v>
       </c>
-    </row>
-    <row r="11" spans="1:8">
+      <c r="H10" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="I10" s="5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
       <c r="A11">
         <v>9</v>
       </c>
@@ -1276,8 +1474,14 @@
       <c r="G11" s="2">
         <v>16</v>
       </c>
-    </row>
-    <row r="12" spans="1:8">
+      <c r="H11" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="I11" s="5">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
       <c r="A12">
         <v>10</v>
       </c>
@@ -1299,8 +1503,14 @@
       <c r="G12" s="2">
         <v>16</v>
       </c>
-    </row>
-    <row r="13" spans="1:8" ht="37.5">
+      <c r="H12" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="I12" s="5">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="37.5">
       <c r="A13">
         <v>11</v>
       </c>
@@ -1322,8 +1532,14 @@
       <c r="G13" s="2">
         <v>10</v>
       </c>
-    </row>
-    <row r="14" spans="1:8" ht="37.5">
+      <c r="H13" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="I13" s="5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="37.5">
       <c r="A14">
         <v>12</v>
       </c>
@@ -1345,11 +1561,17 @@
       <c r="G14" s="2">
         <v>10</v>
       </c>
-      <c r="H14" s="1" t="s">
+      <c r="H14" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="I14" s="5">
+        <v>10</v>
+      </c>
+      <c r="J14" s="1" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="37.5">
+    <row r="15" spans="1:10" ht="37.5">
       <c r="A15">
         <v>13</v>
       </c>
@@ -1371,11 +1593,17 @@
       <c r="G15" s="2">
         <v>16</v>
       </c>
-      <c r="H15" s="1" t="s">
+      <c r="H15" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="I15" s="5">
+        <v>16</v>
+      </c>
+      <c r="J15" s="1" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="37.5">
+    <row r="16" spans="1:10" ht="37.5">
       <c r="A16">
         <v>14</v>
       </c>
@@ -1397,11 +1625,17 @@
       <c r="G16" s="2">
         <v>16</v>
       </c>
-      <c r="H16" s="1" t="s">
+      <c r="H16" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="I16" s="5">
+        <v>16</v>
+      </c>
+      <c r="J16" s="1" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="17" spans="1:8">
+    <row r="17" spans="1:10">
       <c r="A17">
         <v>15</v>
       </c>
@@ -1423,8 +1657,14 @@
       <c r="G17" s="2">
         <v>10</v>
       </c>
-    </row>
-    <row r="18" spans="1:8" ht="37.5">
+      <c r="H17" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="I17" s="5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="37.5">
       <c r="A18">
         <v>16</v>
       </c>
@@ -1446,8 +1686,14 @@
       <c r="G18" s="2">
         <v>10</v>
       </c>
-    </row>
-    <row r="19" spans="1:8">
+      <c r="H18" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="I18" s="5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10">
       <c r="A19">
         <v>17</v>
       </c>
@@ -1469,8 +1715,14 @@
       <c r="G19" s="2">
         <v>16</v>
       </c>
-    </row>
-    <row r="20" spans="1:8">
+      <c r="H19" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="I19" s="5">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10">
       <c r="A20">
         <v>18</v>
       </c>
@@ -1492,8 +1744,14 @@
       <c r="G20" s="2">
         <v>16</v>
       </c>
-    </row>
-    <row r="21" spans="1:8">
+      <c r="H20" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="I20" s="5">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
       <c r="A21">
         <v>19</v>
       </c>
@@ -1515,11 +1773,17 @@
       <c r="G21" s="2">
         <v>24</v>
       </c>
-      <c r="H21" s="1" t="s">
+      <c r="H21" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="I21" s="5">
+        <v>24</v>
+      </c>
+      <c r="J21" s="1" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="22" spans="1:8">
+    <row r="22" spans="1:10">
       <c r="A22">
         <v>20</v>
       </c>
@@ -1541,11 +1805,17 @@
       <c r="G22" s="2">
         <v>24</v>
       </c>
-      <c r="H22" s="1" t="s">
+      <c r="H22" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="I22" s="5">
+        <v>24</v>
+      </c>
+      <c r="J22" s="1" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="23" spans="1:8">
+    <row r="23" spans="1:10">
       <c r="A23">
         <v>21</v>
       </c>
@@ -1567,11 +1837,17 @@
       <c r="G23" s="2">
         <v>24</v>
       </c>
-      <c r="H23" s="1" t="s">
+      <c r="H23" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="I23" s="5">
+        <v>24</v>
+      </c>
+      <c r="J23" s="1" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="24" spans="1:8">
+    <row r="24" spans="1:10">
       <c r="A24">
         <v>22</v>
       </c>
@@ -1593,8 +1869,14 @@
       <c r="G24" s="2">
         <v>24</v>
       </c>
-    </row>
-    <row r="25" spans="1:8">
+      <c r="H24" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="I24" s="5">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10">
       <c r="A25">
         <v>23</v>
       </c>
@@ -1616,8 +1898,14 @@
       <c r="G25" s="2">
         <v>24</v>
       </c>
-    </row>
-    <row r="26" spans="1:8">
+      <c r="H25" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="I25" s="5">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10">
       <c r="A26">
         <v>24</v>
       </c>
@@ -1639,8 +1927,14 @@
       <c r="G26" s="2">
         <v>24</v>
       </c>
-    </row>
-    <row r="27" spans="1:8" ht="37.5">
+      <c r="H26" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="I26" s="5">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" ht="37.5">
       <c r="A27">
         <v>25</v>
       </c>
@@ -1662,11 +1956,17 @@
       <c r="G27" s="2">
         <v>32</v>
       </c>
-      <c r="H27" s="1" t="s">
+      <c r="H27" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="I27" s="5">
+        <v>32</v>
+      </c>
+      <c r="J27" s="1" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="28" spans="1:8" ht="37.5">
+    <row r="28" spans="1:10" ht="37.5">
       <c r="A28">
         <v>26</v>
       </c>
@@ -1688,11 +1988,17 @@
       <c r="G28" s="2">
         <v>32</v>
       </c>
-      <c r="H28" s="1" t="s">
+      <c r="H28" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="I28" s="5">
+        <v>32</v>
+      </c>
+      <c r="J28" s="1" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="29" spans="1:8">
+    <row r="29" spans="1:10">
       <c r="A29">
         <v>27</v>
       </c>
@@ -1714,11 +2020,17 @@
       <c r="G29" s="2">
         <v>14</v>
       </c>
-      <c r="H29" s="1" t="s">
+      <c r="H29" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="I29" s="5">
+        <v>14</v>
+      </c>
+      <c r="J29" s="1" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="30" spans="1:8">
+    <row r="30" spans="1:10">
       <c r="A30">
         <v>28</v>
       </c>
@@ -1740,11 +2052,17 @@
       <c r="G30" s="2">
         <v>14</v>
       </c>
-      <c r="H30" s="1" t="s">
+      <c r="H30" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="I30" s="5">
+        <v>14</v>
+      </c>
+      <c r="J30" s="1" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="31" spans="1:8" ht="37.5">
+    <row r="31" spans="1:10" ht="37.5">
       <c r="A31">
         <v>29</v>
       </c>
@@ -1766,11 +2084,17 @@
       <c r="G31" s="2">
         <v>12</v>
       </c>
-      <c r="H31" s="1" t="s">
+      <c r="H31" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="I31" s="5">
+        <v>12</v>
+      </c>
+      <c r="J31" s="1" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="32" spans="1:8">
+    <row r="32" spans="1:10">
       <c r="A32">
         <v>30</v>
       </c>
@@ -1792,11 +2116,17 @@
       <c r="G32" s="2">
         <v>14</v>
       </c>
-      <c r="H32" s="1" t="s">
+      <c r="H32" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="I32" s="5">
+        <v>14</v>
+      </c>
+      <c r="J32" s="1" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="33" spans="1:8" ht="75">
+    <row r="33" spans="1:10" ht="75">
       <c r="A33">
         <v>31</v>
       </c>
@@ -1818,11 +2148,17 @@
       <c r="G33" s="2">
         <v>14</v>
       </c>
-      <c r="H33" s="1" t="s">
+      <c r="H33" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="I33" s="5">
+        <v>14</v>
+      </c>
+      <c r="J33" s="1" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="34" spans="1:8">
+    <row r="34" spans="1:10">
       <c r="A34">
         <v>32</v>
       </c>
@@ -1844,11 +2180,17 @@
       <c r="G34" s="2">
         <v>14</v>
       </c>
-      <c r="H34" s="1" t="s">
+      <c r="H34" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="I34" s="5">
+        <v>14</v>
+      </c>
+      <c r="J34" s="1" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="35" spans="1:8">
+    <row r="35" spans="1:10">
       <c r="A35">
         <v>33</v>
       </c>
@@ -1870,11 +2212,17 @@
       <c r="G35" s="2">
         <v>14</v>
       </c>
-      <c r="H35" s="1" t="s">
+      <c r="H35" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="I35" s="5">
+        <v>14</v>
+      </c>
+      <c r="J35" s="1" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="36" spans="1:8">
+    <row r="36" spans="1:10">
       <c r="A36">
         <v>34</v>
       </c>
@@ -1896,11 +2244,17 @@
       <c r="G36" s="2">
         <v>14</v>
       </c>
-      <c r="H36" s="1" t="s">
+      <c r="H36" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="I36" s="5">
+        <v>14</v>
+      </c>
+      <c r="J36" s="1" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="37" spans="1:8" ht="37.5">
+    <row r="37" spans="1:10" ht="37.5">
       <c r="A37">
         <v>35</v>
       </c>
@@ -1922,11 +2276,17 @@
       <c r="G37" s="2">
         <v>14</v>
       </c>
-      <c r="H37" s="1" t="s">
+      <c r="H37" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="I37" s="5">
+        <v>14</v>
+      </c>
+      <c r="J37" s="1" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="38" spans="1:8" ht="37.5">
+    <row r="38" spans="1:10" ht="37.5">
       <c r="A38">
         <v>36</v>
       </c>
@@ -1948,11 +2308,17 @@
       <c r="G38" s="2">
         <v>20</v>
       </c>
-      <c r="H38" s="1" t="s">
+      <c r="H38" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="I38" s="5">
+        <v>20</v>
+      </c>
+      <c r="J38" s="1" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="39" spans="1:8">
+    <row r="39" spans="1:10">
       <c r="A39">
         <v>37</v>
       </c>
@@ -1974,8 +2340,14 @@
       <c r="G39" s="2">
         <v>14</v>
       </c>
-    </row>
-    <row r="40" spans="1:8">
+      <c r="H39" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="I39" s="5">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10">
       <c r="A40">
         <v>38</v>
       </c>
@@ -1997,8 +2369,14 @@
       <c r="G40" s="2">
         <v>14</v>
       </c>
-    </row>
-    <row r="41" spans="1:8">
+      <c r="H40" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="I40" s="5">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10">
       <c r="A41">
         <v>39</v>
       </c>
@@ -2020,8 +2398,14 @@
       <c r="G41" s="2">
         <v>14</v>
       </c>
-    </row>
-    <row r="42" spans="1:8" ht="37.5">
+      <c r="H41" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="I41" s="5">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" ht="37.5">
       <c r="A42">
         <v>40</v>
       </c>
@@ -2043,11 +2427,17 @@
       <c r="G42" s="2">
         <v>20</v>
       </c>
-      <c r="H42" s="1" t="s">
+      <c r="H42" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="I42" s="5">
+        <v>20</v>
+      </c>
+      <c r="J42" s="1" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="43" spans="1:8">
+    <row r="43" spans="1:10">
       <c r="A43">
         <v>41</v>
       </c>
@@ -2069,11 +2459,17 @@
       <c r="G43" s="2">
         <v>14</v>
       </c>
-      <c r="H43" s="1" t="s">
+      <c r="H43" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="I43" s="5">
+        <v>14</v>
+      </c>
+      <c r="J43" s="1" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="44" spans="1:8">
+    <row r="44" spans="1:10">
       <c r="A44">
         <v>42</v>
       </c>
@@ -2095,11 +2491,17 @@
       <c r="G44" s="2">
         <v>20</v>
       </c>
-      <c r="H44" s="1" t="s">
+      <c r="H44" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="I44" s="5">
+        <v>20</v>
+      </c>
+      <c r="J44" s="1" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="45" spans="1:8" ht="51">
+    <row r="45" spans="1:10" ht="37.5">
       <c r="A45">
         <v>43</v>
       </c>
@@ -2121,8 +2523,14 @@
       <c r="G45" s="2">
         <v>10</v>
       </c>
-    </row>
-    <row r="46" spans="1:8" ht="51">
+      <c r="H45" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="I45" s="5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" ht="37.5">
       <c r="A46">
         <v>44</v>
       </c>
@@ -2144,8 +2552,14 @@
       <c r="G46" s="2">
         <v>10</v>
       </c>
-    </row>
-    <row r="47" spans="1:8" ht="37.5">
+      <c r="H46" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="I46" s="5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" ht="37.5">
       <c r="A47">
         <v>45</v>
       </c>
@@ -2167,11 +2581,17 @@
       <c r="G47" s="2">
         <v>16</v>
       </c>
-      <c r="H47" s="1" t="s">
+      <c r="H47" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="I47" s="5">
+        <v>16</v>
+      </c>
+      <c r="J47" s="1" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="48" spans="1:8" ht="37.5">
+    <row r="48" spans="1:10" ht="37.5">
       <c r="A48">
         <v>46</v>
       </c>
@@ -2193,11 +2613,17 @@
       <c r="G48" s="2">
         <v>16</v>
       </c>
-      <c r="H48" s="1" t="s">
+      <c r="H48" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="I48" s="5">
+        <v>16</v>
+      </c>
+      <c r="J48" s="1" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="49" spans="1:8" ht="37.5">
+    <row r="49" spans="1:10" ht="37.5">
       <c r="A49">
         <v>47</v>
       </c>
@@ -2219,11 +2645,17 @@
       <c r="G49" s="2">
         <v>16</v>
       </c>
-      <c r="H49" s="1" t="s">
+      <c r="H49" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="I49" s="5">
+        <v>16</v>
+      </c>
+      <c r="J49" s="1" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="50" spans="1:8" ht="37.5">
+    <row r="50" spans="1:10" ht="37.5">
       <c r="A50">
         <v>48</v>
       </c>
@@ -2245,11 +2677,17 @@
       <c r="G50" s="2">
         <v>16</v>
       </c>
-      <c r="H50" s="1" t="s">
+      <c r="H50" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="I50" s="5">
+        <v>16</v>
+      </c>
+      <c r="J50" s="1" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="51" spans="1:8">
+    <row r="51" spans="1:10">
       <c r="A51">
         <v>49</v>
       </c>
@@ -2271,19 +2709,43 @@
       <c r="G51" s="2">
         <v>10</v>
       </c>
-    </row>
-    <row r="52" spans="1:8">
+      <c r="H51" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="I51" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10">
       <c r="A52">
         <v>50</v>
       </c>
+      <c r="B52" t="s">
+        <v>170</v>
+      </c>
       <c r="C52">
-        <v>14</v>
+        <v>10</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>170</v>
       </c>
       <c r="E52">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="53" spans="1:8">
+        <v>10</v>
+      </c>
+      <c r="F52" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G52">
+        <v>10</v>
+      </c>
+      <c r="H52" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="I52">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10">
       <c r="A53">
         <v>51</v>
       </c>
@@ -2294,7 +2756,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="54" spans="1:8">
+    <row r="54" spans="1:10">
       <c r="A54">
         <v>52</v>
       </c>
@@ -2305,7 +2767,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="55" spans="1:8">
+    <row r="55" spans="1:10">
       <c r="A55">
         <v>53</v>
       </c>
@@ -2316,7 +2778,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="56" spans="1:8">
+    <row r="56" spans="1:10">
       <c r="A56">
         <v>54</v>
       </c>
@@ -2327,7 +2789,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="57" spans="1:8">
+    <row r="57" spans="1:10">
       <c r="A57">
         <v>55</v>
       </c>
@@ -2338,7 +2800,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="58" spans="1:8">
+    <row r="58" spans="1:10">
       <c r="A58">
         <v>56</v>
       </c>
@@ -2349,7 +2811,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="59" spans="1:8">
+    <row r="59" spans="1:10">
       <c r="A59">
         <v>57</v>
       </c>
@@ -2360,7 +2822,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="60" spans="1:8">
+    <row r="60" spans="1:10">
       <c r="A60">
         <v>58</v>
       </c>
@@ -2371,7 +2833,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="61" spans="1:8">
+    <row r="61" spans="1:10">
       <c r="A61">
         <v>59</v>
       </c>
@@ -2382,7 +2844,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="62" spans="1:8">
+    <row r="62" spans="1:10">
       <c r="A62">
         <v>60</v>
       </c>
@@ -2393,7 +2855,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="63" spans="1:8">
+    <row r="63" spans="1:10">
       <c r="A63">
         <v>61</v>
       </c>
@@ -2404,7 +2866,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="64" spans="1:8">
+    <row r="64" spans="1:10">
       <c r="A64">
         <v>62</v>
       </c>

--- a/Assets/Originals/Excels/Button/ButtonMessage.xlsx
+++ b/Assets/Originals/Excels/Button/ButtonMessage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\Button\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52D1FD82-60B0-4D0F-AD8B-75F9EA2B5F5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D66847A-F68C-4B04-8132-D13A05F29957}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="210">
   <si>
     <t>number</t>
     <phoneticPr fontId="1"/>
@@ -777,6 +777,123 @@
       <t>語</t>
     </r>
     <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>messageSpanish</t>
+  </si>
+  <si>
+    <t>Iniciar partida</t>
+  </si>
+  <si>
+    <t>Opciones</t>
+  </si>
+  <si>
+    <t>Salir del juego</t>
+  </si>
+  <si>
+    <t>Volver</t>
+  </si>
+  <si>
+    <t>Sensibilidad</t>
+  </si>
+  <si>
+    <t>Música</t>
+  </si>
+  <si>
+    <t>Efectos</t>
+  </si>
+  <si>
+    <t>Brillo</t>
+  </si>
+  <si>
+    <t>Modo de pantalla</t>
+  </si>
+  <si>
+    <t>Pantalla completa</t>
+  </si>
+  <si>
+    <t>Ventana</t>
+  </si>
+  <si>
+    <t>Resolución</t>
+  </si>
+  <si>
+    <t>Controles</t>
+  </si>
+  <si>
+    <t>Mostrar</t>
+  </si>
+  <si>
+    <t>Ocultar</t>
+  </si>
+  <si>
+    <t>Descripción de objetos</t>
+  </si>
+  <si>
+    <t>Descripción de la brújula</t>
+  </si>
+  <si>
+    <t>Ajuste de volumen</t>
+  </si>
+  <si>
+    <t>Pantalla</t>
+  </si>
+  <si>
+    <t>Explicación</t>
+  </si>
+  <si>
+    <t>Idioma</t>
+  </si>
+  <si>
+    <t>Sí</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Documento</t>
+  </si>
+  <si>
+    <t>Objeto Misterioso</t>
+  </si>
+  <si>
+    <t>Continuar</t>
+  </si>
+  <si>
+    <t>Revisar objetos</t>
+  </si>
+  <si>
+    <t>Volver al título</t>
+  </si>
+  <si>
+    <t>Laberinto de la Prisión Fantasma</t>
+  </si>
+  <si>
+    <t>Ensueño</t>
+  </si>
+  <si>
+    <t>Fantasía</t>
+  </si>
+  <si>
+    <t>Pesadilla</t>
+  </si>
+  <si>
+    <t>Reiniciar</t>
+  </si>
+  <si>
+    <t>¡Haz clic aquí
+para la encuesta!</t>
+  </si>
+  <si>
+    <t>¡Haz clic aquí
+para la lista de deseos!</t>
+  </si>
+  <si>
+    <t>messageSizeSpanish</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Spanish</t>
   </si>
 </sst>
 </file>
@@ -1136,7 +1253,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J102"/>
+  <dimension ref="A1:L102"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="2" max="2" width="51.25" customWidth="1"/>
@@ -1147,10 +1264,12 @@
     <col min="7" max="7" width="24.875" customWidth="1"/>
     <col min="8" max="8" width="22.25" customWidth="1"/>
     <col min="9" max="9" width="22.5" customWidth="1"/>
-    <col min="10" max="10" width="24.375" style="1" customWidth="1"/>
+    <col min="10" max="10" width="19.125" customWidth="1"/>
+    <col min="11" max="11" width="21.75" customWidth="1"/>
+    <col min="12" max="12" width="24.375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:12">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1178,11 +1297,17 @@
       <c r="I1" t="s">
         <v>169</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" t="s">
+        <v>172</v>
+      </c>
+      <c r="K1" t="s">
+        <v>208</v>
+      </c>
+      <c r="L1" s="1" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:12">
       <c r="A2">
         <v>0</v>
       </c>
@@ -1210,8 +1335,14 @@
       <c r="I2" s="5">
         <v>14</v>
       </c>
-    </row>
-    <row r="3" spans="1:10" ht="37.5">
+      <c r="J2" t="s">
+        <v>173</v>
+      </c>
+      <c r="K2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="37.5">
       <c r="A3">
         <v>1</v>
       </c>
@@ -1239,11 +1370,17 @@
       <c r="I3" s="5">
         <v>14</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="J3" t="s">
+        <v>174</v>
+      </c>
+      <c r="K3">
+        <v>14</v>
+      </c>
+      <c r="L3" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:12">
       <c r="A4">
         <v>2</v>
       </c>
@@ -1271,8 +1408,14 @@
       <c r="I4" s="5">
         <v>14</v>
       </c>
-    </row>
-    <row r="5" spans="1:10" ht="37.5">
+      <c r="J4" t="s">
+        <v>175</v>
+      </c>
+      <c r="K4">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="37.5">
       <c r="A5">
         <v>3</v>
       </c>
@@ -1300,11 +1443,17 @@
       <c r="I5" s="5">
         <v>24</v>
       </c>
-      <c r="J5" s="1" t="s">
+      <c r="J5" t="s">
+        <v>176</v>
+      </c>
+      <c r="K5">
+        <v>24</v>
+      </c>
+      <c r="L5" s="1" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:12">
       <c r="A6">
         <v>4</v>
       </c>
@@ -1332,11 +1481,17 @@
       <c r="I6" s="5">
         <v>14</v>
       </c>
-      <c r="J6" s="1" t="s">
+      <c r="J6" t="s">
+        <v>177</v>
+      </c>
+      <c r="K6">
+        <v>14</v>
+      </c>
+      <c r="L6" s="1" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:12">
       <c r="A7">
         <v>5</v>
       </c>
@@ -1364,8 +1519,14 @@
       <c r="I7" s="5">
         <v>14</v>
       </c>
-    </row>
-    <row r="8" spans="1:10">
+      <c r="J7" t="s">
+        <v>178</v>
+      </c>
+      <c r="K7">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12">
       <c r="A8">
         <v>6</v>
       </c>
@@ -1393,8 +1554,14 @@
       <c r="I8" s="5">
         <v>14</v>
       </c>
-    </row>
-    <row r="9" spans="1:10">
+      <c r="J8" t="s">
+        <v>179</v>
+      </c>
+      <c r="K8">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12">
       <c r="A9">
         <v>7</v>
       </c>
@@ -1422,8 +1589,14 @@
       <c r="I9" s="5">
         <v>12</v>
       </c>
-    </row>
-    <row r="10" spans="1:10" ht="37.5">
+      <c r="J9" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="K9">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="37.5">
       <c r="A10">
         <v>8</v>
       </c>
@@ -1451,8 +1624,14 @@
       <c r="I10" s="5">
         <v>10</v>
       </c>
-    </row>
-    <row r="11" spans="1:10">
+      <c r="J10" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="K10">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="37.5">
       <c r="A11">
         <v>9</v>
       </c>
@@ -1480,8 +1659,14 @@
       <c r="I11" s="5">
         <v>16</v>
       </c>
-    </row>
-    <row r="12" spans="1:10">
+      <c r="J11" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="K11">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12">
       <c r="A12">
         <v>10</v>
       </c>
@@ -1509,8 +1694,14 @@
       <c r="I12" s="5">
         <v>16</v>
       </c>
-    </row>
-    <row r="13" spans="1:10" ht="37.5">
+      <c r="J12" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="K12">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="37.5">
       <c r="A13">
         <v>11</v>
       </c>
@@ -1538,8 +1729,14 @@
       <c r="I13" s="5">
         <v>10</v>
       </c>
-    </row>
-    <row r="14" spans="1:10" ht="37.5">
+      <c r="J13" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="K13">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="37.5">
       <c r="A14">
         <v>12</v>
       </c>
@@ -1568,10 +1765,16 @@
         <v>10</v>
       </c>
       <c r="J14" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="K14">
+        <v>8</v>
+      </c>
+      <c r="L14" s="1" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="15" spans="1:10" ht="37.5">
+    <row r="15" spans="1:12" ht="37.5">
       <c r="A15">
         <v>13</v>
       </c>
@@ -1600,10 +1803,16 @@
         <v>16</v>
       </c>
       <c r="J15" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="K15">
+        <v>16</v>
+      </c>
+      <c r="L15" s="1" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="16" spans="1:10" ht="37.5">
+    <row r="16" spans="1:12" ht="37.5">
       <c r="A16">
         <v>14</v>
       </c>
@@ -1632,10 +1841,16 @@
         <v>16</v>
       </c>
       <c r="J16" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="K16">
+        <v>16</v>
+      </c>
+      <c r="L16" s="1" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="17" spans="1:10">
+    <row r="17" spans="1:12" ht="56.25">
       <c r="A17">
         <v>15</v>
       </c>
@@ -1663,8 +1878,14 @@
       <c r="I17" s="5">
         <v>10</v>
       </c>
-    </row>
-    <row r="18" spans="1:10" ht="37.5">
+      <c r="J17" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="K17">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" ht="56.25">
       <c r="A18">
         <v>16</v>
       </c>
@@ -1692,8 +1913,14 @@
       <c r="I18" s="5">
         <v>10</v>
       </c>
-    </row>
-    <row r="19" spans="1:10">
+      <c r="J18" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="K18">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12">
       <c r="A19">
         <v>17</v>
       </c>
@@ -1721,8 +1948,14 @@
       <c r="I19" s="5">
         <v>16</v>
       </c>
-    </row>
-    <row r="20" spans="1:10">
+      <c r="J19" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="K19">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12">
       <c r="A20">
         <v>18</v>
       </c>
@@ -1750,8 +1983,14 @@
       <c r="I20" s="5">
         <v>16</v>
       </c>
-    </row>
-    <row r="21" spans="1:10">
+      <c r="J20" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="K20">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" ht="37.5">
       <c r="A21">
         <v>19</v>
       </c>
@@ -1780,10 +2019,16 @@
         <v>24</v>
       </c>
       <c r="J21" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="K21">
+        <v>18</v>
+      </c>
+      <c r="L21" s="1" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="22" spans="1:10">
+    <row r="22" spans="1:12" ht="37.5">
       <c r="A22">
         <v>20</v>
       </c>
@@ -1812,10 +2057,16 @@
         <v>24</v>
       </c>
       <c r="J22" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="K22">
+        <v>18</v>
+      </c>
+      <c r="L22" s="1" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="23" spans="1:10">
+    <row r="23" spans="1:12">
       <c r="A23">
         <v>21</v>
       </c>
@@ -1844,10 +2095,16 @@
         <v>24</v>
       </c>
       <c r="J23" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="K23">
+        <v>18</v>
+      </c>
+      <c r="L23" s="1" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="24" spans="1:10">
+    <row r="24" spans="1:12">
       <c r="A24">
         <v>22</v>
       </c>
@@ -1875,8 +2132,14 @@
       <c r="I24" s="5">
         <v>24</v>
       </c>
-    </row>
-    <row r="25" spans="1:10">
+      <c r="J24" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="K24">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" ht="37.5">
       <c r="A25">
         <v>23</v>
       </c>
@@ -1904,8 +2167,14 @@
       <c r="I25" s="5">
         <v>24</v>
       </c>
-    </row>
-    <row r="26" spans="1:10">
+      <c r="J25" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="K25">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12">
       <c r="A26">
         <v>24</v>
       </c>
@@ -1933,8 +2202,14 @@
       <c r="I26" s="5">
         <v>24</v>
       </c>
-    </row>
-    <row r="27" spans="1:10" ht="37.5">
+      <c r="J26" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="K26">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" ht="37.5">
       <c r="A27">
         <v>25</v>
       </c>
@@ -1963,10 +2238,16 @@
         <v>32</v>
       </c>
       <c r="J27" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="K27">
+        <v>32</v>
+      </c>
+      <c r="L27" s="1" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="28" spans="1:10" ht="37.5">
+    <row r="28" spans="1:12" ht="37.5">
       <c r="A28">
         <v>26</v>
       </c>
@@ -1995,10 +2276,16 @@
         <v>32</v>
       </c>
       <c r="J28" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="K28">
+        <v>32</v>
+      </c>
+      <c r="L28" s="1" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="29" spans="1:10">
+    <row r="29" spans="1:12">
       <c r="A29">
         <v>27</v>
       </c>
@@ -2027,10 +2314,16 @@
         <v>14</v>
       </c>
       <c r="J29" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="K29">
+        <v>14</v>
+      </c>
+      <c r="L29" s="1" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="30" spans="1:10">
+    <row r="30" spans="1:12">
       <c r="A30">
         <v>28</v>
       </c>
@@ -2059,10 +2352,16 @@
         <v>14</v>
       </c>
       <c r="J30" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="K30">
+        <v>14</v>
+      </c>
+      <c r="L30" s="1" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="31" spans="1:10" ht="37.5">
+    <row r="31" spans="1:12" ht="37.5">
       <c r="A31">
         <v>29</v>
       </c>
@@ -2091,10 +2390,16 @@
         <v>12</v>
       </c>
       <c r="J31" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="K31">
+        <v>12</v>
+      </c>
+      <c r="L31" s="1" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="32" spans="1:10">
+    <row r="32" spans="1:12" ht="37.5">
       <c r="A32">
         <v>30</v>
       </c>
@@ -2123,10 +2428,16 @@
         <v>14</v>
       </c>
       <c r="J32" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="K32">
+        <v>14</v>
+      </c>
+      <c r="L32" s="1" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="33" spans="1:10" ht="75">
+    <row r="33" spans="1:12" ht="75">
       <c r="A33">
         <v>31</v>
       </c>
@@ -2155,10 +2466,16 @@
         <v>14</v>
       </c>
       <c r="J33" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="K33">
+        <v>14</v>
+      </c>
+      <c r="L33" s="1" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="34" spans="1:10">
+    <row r="34" spans="1:12" ht="56.25">
       <c r="A34">
         <v>32</v>
       </c>
@@ -2187,10 +2504,16 @@
         <v>14</v>
       </c>
       <c r="J34" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="K34">
+        <v>14</v>
+      </c>
+      <c r="L34" s="1" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="35" spans="1:10">
+    <row r="35" spans="1:12">
       <c r="A35">
         <v>33</v>
       </c>
@@ -2219,10 +2542,16 @@
         <v>14</v>
       </c>
       <c r="J35" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="K35">
+        <v>14</v>
+      </c>
+      <c r="L35" s="1" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="36" spans="1:10">
+    <row r="36" spans="1:12" ht="37.5">
       <c r="A36">
         <v>34</v>
       </c>
@@ -2251,10 +2580,16 @@
         <v>14</v>
       </c>
       <c r="J36" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="K36">
+        <v>14</v>
+      </c>
+      <c r="L36" s="1" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="37" spans="1:10" ht="37.5">
+    <row r="37" spans="1:12" ht="37.5">
       <c r="A37">
         <v>35</v>
       </c>
@@ -2283,10 +2618,16 @@
         <v>14</v>
       </c>
       <c r="J37" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="K37">
+        <v>14</v>
+      </c>
+      <c r="L37" s="1" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="38" spans="1:10" ht="37.5">
+    <row r="38" spans="1:12" ht="93.75">
       <c r="A38">
         <v>36</v>
       </c>
@@ -2315,10 +2656,16 @@
         <v>20</v>
       </c>
       <c r="J38" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="K38">
+        <v>16</v>
+      </c>
+      <c r="L38" s="1" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="39" spans="1:10">
+    <row r="39" spans="1:12">
       <c r="A39">
         <v>37</v>
       </c>
@@ -2346,8 +2693,14 @@
       <c r="I39" s="5">
         <v>14</v>
       </c>
-    </row>
-    <row r="40" spans="1:10">
+      <c r="J39" t="s">
+        <v>202</v>
+      </c>
+      <c r="K39">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12">
       <c r="A40">
         <v>38</v>
       </c>
@@ -2375,8 +2728,14 @@
       <c r="I40" s="5">
         <v>14</v>
       </c>
-    </row>
-    <row r="41" spans="1:10">
+      <c r="J40" t="s">
+        <v>203</v>
+      </c>
+      <c r="K40">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12">
       <c r="A41">
         <v>39</v>
       </c>
@@ -2404,8 +2763,14 @@
       <c r="I41" s="5">
         <v>14</v>
       </c>
-    </row>
-    <row r="42" spans="1:10" ht="37.5">
+      <c r="J41" t="s">
+        <v>204</v>
+      </c>
+      <c r="K41">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" ht="37.5">
       <c r="A42">
         <v>40</v>
       </c>
@@ -2433,11 +2798,17 @@
       <c r="I42" s="5">
         <v>20</v>
       </c>
-      <c r="J42" s="1" t="s">
+      <c r="J42" t="s">
+        <v>176</v>
+      </c>
+      <c r="K42">
+        <v>16</v>
+      </c>
+      <c r="L42" s="1" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="43" spans="1:10">
+    <row r="43" spans="1:12">
       <c r="A43">
         <v>41</v>
       </c>
@@ -2465,11 +2836,17 @@
       <c r="I43" s="5">
         <v>14</v>
       </c>
-      <c r="J43" s="1" t="s">
+      <c r="J43" t="s">
+        <v>205</v>
+      </c>
+      <c r="K43">
+        <v>14</v>
+      </c>
+      <c r="L43" s="1" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="44" spans="1:10">
+    <row r="44" spans="1:12" ht="37.5">
       <c r="A44">
         <v>42</v>
       </c>
@@ -2498,10 +2875,16 @@
         <v>20</v>
       </c>
       <c r="J44" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="K44">
+        <v>20</v>
+      </c>
+      <c r="L44" s="1" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="45" spans="1:10" ht="37.5">
+    <row r="45" spans="1:12" ht="93.75">
       <c r="A45">
         <v>43</v>
       </c>
@@ -2529,8 +2912,14 @@
       <c r="I45" s="5">
         <v>10</v>
       </c>
-    </row>
-    <row r="46" spans="1:10" ht="37.5">
+      <c r="J45" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="K45">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12" ht="93.75">
       <c r="A46">
         <v>44</v>
       </c>
@@ -2558,8 +2947,14 @@
       <c r="I46" s="5">
         <v>10</v>
       </c>
-    </row>
-    <row r="47" spans="1:10" ht="37.5">
+      <c r="J46" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="K46">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12" ht="37.5">
       <c r="A47">
         <v>45</v>
       </c>
@@ -2588,10 +2983,16 @@
         <v>16</v>
       </c>
       <c r="J47" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="K47">
+        <v>16</v>
+      </c>
+      <c r="L47" s="1" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="48" spans="1:10" ht="37.5">
+    <row r="48" spans="1:12" ht="37.5">
       <c r="A48">
         <v>46</v>
       </c>
@@ -2620,10 +3021,16 @@
         <v>16</v>
       </c>
       <c r="J48" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="K48">
+        <v>16</v>
+      </c>
+      <c r="L48" s="1" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="49" spans="1:10" ht="37.5">
+    <row r="49" spans="1:12" ht="37.5">
       <c r="A49">
         <v>47</v>
       </c>
@@ -2652,10 +3059,16 @@
         <v>16</v>
       </c>
       <c r="J49" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="K49">
+        <v>16</v>
+      </c>
+      <c r="L49" s="1" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="50" spans="1:10" ht="37.5">
+    <row r="50" spans="1:12" ht="37.5">
       <c r="A50">
         <v>48</v>
       </c>
@@ -2684,10 +3097,16 @@
         <v>16</v>
       </c>
       <c r="J50" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="K50">
+        <v>16</v>
+      </c>
+      <c r="L50" s="1" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="51" spans="1:10">
+    <row r="51" spans="1:12">
       <c r="A51">
         <v>49</v>
       </c>
@@ -2715,8 +3134,14 @@
       <c r="I51" s="2">
         <v>10</v>
       </c>
-    </row>
-    <row r="52" spans="1:10">
+      <c r="J51" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="K51" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12">
       <c r="A52">
         <v>50</v>
       </c>
@@ -2744,19 +3169,49 @@
       <c r="I52">
         <v>10</v>
       </c>
-    </row>
-    <row r="53" spans="1:10">
+      <c r="J52" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="K52" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12">
       <c r="A53">
         <v>51</v>
       </c>
+      <c r="B53" t="s">
+        <v>209</v>
+      </c>
       <c r="C53">
         <v>14</v>
       </c>
+      <c r="D53" t="s">
+        <v>209</v>
+      </c>
       <c r="E53">
         <v>14</v>
       </c>
-    </row>
-    <row r="54" spans="1:10">
+      <c r="F53" t="s">
+        <v>209</v>
+      </c>
+      <c r="G53">
+        <v>14</v>
+      </c>
+      <c r="H53" t="s">
+        <v>209</v>
+      </c>
+      <c r="I53">
+        <v>14</v>
+      </c>
+      <c r="J53" t="s">
+        <v>209</v>
+      </c>
+      <c r="K53">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12">
       <c r="A54">
         <v>52</v>
       </c>
@@ -2767,7 +3222,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="55" spans="1:10">
+    <row r="55" spans="1:12">
       <c r="A55">
         <v>53</v>
       </c>
@@ -2778,7 +3233,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="56" spans="1:10">
+    <row r="56" spans="1:12">
       <c r="A56">
         <v>54</v>
       </c>
@@ -2789,7 +3244,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="57" spans="1:10">
+    <row r="57" spans="1:12">
       <c r="A57">
         <v>55</v>
       </c>
@@ -2800,7 +3255,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="58" spans="1:10">
+    <row r="58" spans="1:12">
       <c r="A58">
         <v>56</v>
       </c>
@@ -2811,7 +3266,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="59" spans="1:10">
+    <row r="59" spans="1:12">
       <c r="A59">
         <v>57</v>
       </c>
@@ -2822,7 +3277,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="60" spans="1:10">
+    <row r="60" spans="1:12">
       <c r="A60">
         <v>58</v>
       </c>
@@ -2833,7 +3288,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="61" spans="1:10">
+    <row r="61" spans="1:12">
       <c r="A61">
         <v>59</v>
       </c>
@@ -2844,7 +3299,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="62" spans="1:10">
+    <row r="62" spans="1:12">
       <c r="A62">
         <v>60</v>
       </c>
@@ -2855,7 +3310,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="63" spans="1:10">
+    <row r="63" spans="1:12">
       <c r="A63">
         <v>61</v>
       </c>
@@ -2866,7 +3321,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="64" spans="1:10">
+    <row r="64" spans="1:12">
       <c r="A64">
         <v>62</v>
       </c>

--- a/Assets/Originals/Excels/Button/ButtonMessage.xlsx
+++ b/Assets/Originals/Excels/Button/ButtonMessage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\Button\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D66847A-F68C-4B04-8132-D13A05F29957}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D5C5A2A-6CE7-4024-AC15-F28033AF30B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="359" uniqueCount="241">
   <si>
     <t>number</t>
     <phoneticPr fontId="1"/>
@@ -894,6 +894,103 @@
   </si>
   <si>
     <t>Spanish</t>
+  </si>
+  <si>
+    <t>messageSizePortuguese</t>
+  </si>
+  <si>
+    <t>Iniciar jogo</t>
+  </si>
+  <si>
+    <t>Opções</t>
+  </si>
+  <si>
+    <t>Sair do jogo</t>
+  </si>
+  <si>
+    <t>Voltar</t>
+  </si>
+  <si>
+    <t>Sensibilidade</t>
+  </si>
+  <si>
+    <t>Efeitos</t>
+  </si>
+  <si>
+    <t>Brilho</t>
+  </si>
+  <si>
+    <t>Modo de tela</t>
+  </si>
+  <si>
+    <t>Tela cheia</t>
+  </si>
+  <si>
+    <t>Janela</t>
+  </si>
+  <si>
+    <t>Resolução</t>
+  </si>
+  <si>
+    <t>Instruções de controle</t>
+  </si>
+  <si>
+    <t>Descrição dos itens</t>
+  </si>
+  <si>
+    <t>Descrição da bússola</t>
+  </si>
+  <si>
+    <t>Ajuste de volume</t>
+  </si>
+  <si>
+    <t>Tela</t>
+  </si>
+  <si>
+    <t>Explicação</t>
+  </si>
+  <si>
+    <t>Sim</t>
+  </si>
+  <si>
+    <t>Não</t>
+  </si>
+  <si>
+    <t>Item Misterioso</t>
+  </si>
+  <si>
+    <t>Verificar itens</t>
+  </si>
+  <si>
+    <t>Voltar ao título</t>
+  </si>
+  <si>
+    <t>Labirinto da Prisão Fantasma</t>
+  </si>
+  <si>
+    <t>Devaneio</t>
+  </si>
+  <si>
+    <t>Fantasia</t>
+  </si>
+  <si>
+    <t>Pesadelo</t>
+  </si>
+  <si>
+    <t>Clique aqui
+para a pesquisa!</t>
+  </si>
+  <si>
+    <t>Clique aqui
+para a lista de desejos!</t>
+  </si>
+  <si>
+    <t>messagePortuguese</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Portuguese</t>
+    <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
@@ -1253,7 +1350,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L102"/>
+  <dimension ref="A1:N102"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="2" max="2" width="51.25" customWidth="1"/>
@@ -1266,10 +1363,12 @@
     <col min="9" max="9" width="22.5" customWidth="1"/>
     <col min="10" max="10" width="19.125" customWidth="1"/>
     <col min="11" max="11" width="21.75" customWidth="1"/>
-    <col min="12" max="12" width="24.375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="19.5" customWidth="1"/>
+    <col min="13" max="13" width="24" customWidth="1"/>
+    <col min="14" max="14" width="24.375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:14">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1303,11 +1402,17 @@
       <c r="K1" t="s">
         <v>208</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" t="s">
+        <v>239</v>
+      </c>
+      <c r="M1" t="s">
+        <v>210</v>
+      </c>
+      <c r="N1" s="1" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="2" spans="1:12">
+    <row r="2" spans="1:14">
       <c r="A2">
         <v>0</v>
       </c>
@@ -1341,8 +1446,14 @@
       <c r="K2">
         <v>14</v>
       </c>
-    </row>
-    <row r="3" spans="1:12" ht="37.5">
+      <c r="L2" t="s">
+        <v>211</v>
+      </c>
+      <c r="M2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="37.5">
       <c r="A3">
         <v>1</v>
       </c>
@@ -1376,11 +1487,17 @@
       <c r="K3">
         <v>14</v>
       </c>
-      <c r="L3" s="1" t="s">
+      <c r="L3" t="s">
+        <v>212</v>
+      </c>
+      <c r="M3">
+        <v>14</v>
+      </c>
+      <c r="N3" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="4" spans="1:12">
+    <row r="4" spans="1:14">
       <c r="A4">
         <v>2</v>
       </c>
@@ -1414,8 +1531,14 @@
       <c r="K4">
         <v>14</v>
       </c>
-    </row>
-    <row r="5" spans="1:12" ht="37.5">
+      <c r="L4" t="s">
+        <v>213</v>
+      </c>
+      <c r="M4">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="37.5">
       <c r="A5">
         <v>3</v>
       </c>
@@ -1449,11 +1572,17 @@
       <c r="K5">
         <v>24</v>
       </c>
-      <c r="L5" s="1" t="s">
+      <c r="L5" t="s">
+        <v>214</v>
+      </c>
+      <c r="M5">
+        <v>24</v>
+      </c>
+      <c r="N5" s="1" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="6" spans="1:12">
+    <row r="6" spans="1:14">
       <c r="A6">
         <v>4</v>
       </c>
@@ -1487,11 +1616,17 @@
       <c r="K6">
         <v>14</v>
       </c>
-      <c r="L6" s="1" t="s">
+      <c r="L6" t="s">
+        <v>215</v>
+      </c>
+      <c r="M6">
+        <v>14</v>
+      </c>
+      <c r="N6" s="1" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="7" spans="1:12">
+    <row r="7" spans="1:14">
       <c r="A7">
         <v>5</v>
       </c>
@@ -1525,8 +1660,14 @@
       <c r="K7">
         <v>14</v>
       </c>
-    </row>
-    <row r="8" spans="1:12">
+      <c r="L7" t="s">
+        <v>178</v>
+      </c>
+      <c r="M7">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
       <c r="A8">
         <v>6</v>
       </c>
@@ -1560,8 +1701,14 @@
       <c r="K8">
         <v>14</v>
       </c>
-    </row>
-    <row r="9" spans="1:12">
+      <c r="L8" t="s">
+        <v>216</v>
+      </c>
+      <c r="M8">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
       <c r="A9">
         <v>7</v>
       </c>
@@ -1595,8 +1742,14 @@
       <c r="K9">
         <v>12</v>
       </c>
-    </row>
-    <row r="10" spans="1:12" ht="37.5">
+      <c r="L9" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="M9">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="37.5">
       <c r="A10">
         <v>8</v>
       </c>
@@ -1630,8 +1783,14 @@
       <c r="K10">
         <v>10</v>
       </c>
-    </row>
-    <row r="11" spans="1:12" ht="37.5">
+      <c r="L10" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="M10">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
       <c r="A11">
         <v>9</v>
       </c>
@@ -1665,8 +1824,14 @@
       <c r="K11">
         <v>16</v>
       </c>
-    </row>
-    <row r="12" spans="1:12">
+      <c r="L11" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="M11">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
       <c r="A12">
         <v>10</v>
       </c>
@@ -1700,8 +1865,14 @@
       <c r="K12">
         <v>16</v>
       </c>
-    </row>
-    <row r="13" spans="1:12" ht="37.5">
+      <c r="L12" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="M12">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="37.5">
       <c r="A13">
         <v>11</v>
       </c>
@@ -1735,8 +1906,14 @@
       <c r="K13">
         <v>10</v>
       </c>
-    </row>
-    <row r="14" spans="1:12" ht="37.5">
+      <c r="L13" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="M13">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="37.5">
       <c r="A14">
         <v>12</v>
       </c>
@@ -1771,10 +1948,16 @@
         <v>8</v>
       </c>
       <c r="L14" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="M14">
+        <v>8</v>
+      </c>
+      <c r="N14" s="1" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="15" spans="1:12" ht="37.5">
+    <row r="15" spans="1:14" ht="37.5">
       <c r="A15">
         <v>13</v>
       </c>
@@ -1809,10 +1992,16 @@
         <v>16</v>
       </c>
       <c r="L15" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="M15">
+        <v>16</v>
+      </c>
+      <c r="N15" s="1" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="16" spans="1:12" ht="37.5">
+    <row r="16" spans="1:14" ht="37.5">
       <c r="A16">
         <v>14</v>
       </c>
@@ -1847,10 +2036,16 @@
         <v>16</v>
       </c>
       <c r="L16" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="M16">
+        <v>16</v>
+      </c>
+      <c r="N16" s="1" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="17" spans="1:12" ht="56.25">
+    <row r="17" spans="1:14" ht="37.5">
       <c r="A17">
         <v>15</v>
       </c>
@@ -1884,8 +2079,14 @@
       <c r="K17">
         <v>10</v>
       </c>
-    </row>
-    <row r="18" spans="1:12" ht="56.25">
+      <c r="L17" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="M17">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" ht="37.5">
       <c r="A18">
         <v>16</v>
       </c>
@@ -1919,8 +2120,14 @@
       <c r="K18">
         <v>8</v>
       </c>
-    </row>
-    <row r="19" spans="1:12">
+      <c r="L18" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="M18">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14">
       <c r="A19">
         <v>17</v>
       </c>
@@ -1954,8 +2161,14 @@
       <c r="K19">
         <v>16</v>
       </c>
-    </row>
-    <row r="20" spans="1:12">
+      <c r="L19" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="M19">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14">
       <c r="A20">
         <v>18</v>
       </c>
@@ -1989,8 +2202,14 @@
       <c r="K20">
         <v>16</v>
       </c>
-    </row>
-    <row r="21" spans="1:12" ht="37.5">
+      <c r="L20" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="M20">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14">
       <c r="A21">
         <v>19</v>
       </c>
@@ -2025,10 +2244,16 @@
         <v>18</v>
       </c>
       <c r="L21" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="M21">
+        <v>18</v>
+      </c>
+      <c r="N21" s="1" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="22" spans="1:12" ht="37.5">
+    <row r="22" spans="1:14">
       <c r="A22">
         <v>20</v>
       </c>
@@ -2063,10 +2288,16 @@
         <v>18</v>
       </c>
       <c r="L22" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="M22">
+        <v>18</v>
+      </c>
+      <c r="N22" s="1" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="23" spans="1:12">
+    <row r="23" spans="1:14">
       <c r="A23">
         <v>21</v>
       </c>
@@ -2101,10 +2332,16 @@
         <v>18</v>
       </c>
       <c r="L23" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="M23">
+        <v>18</v>
+      </c>
+      <c r="N23" s="1" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="24" spans="1:12">
+    <row r="24" spans="1:14">
       <c r="A24">
         <v>22</v>
       </c>
@@ -2138,8 +2375,14 @@
       <c r="K24">
         <v>18</v>
       </c>
-    </row>
-    <row r="25" spans="1:12" ht="37.5">
+      <c r="L24" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="M24">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14">
       <c r="A25">
         <v>23</v>
       </c>
@@ -2173,8 +2416,14 @@
       <c r="K25">
         <v>18</v>
       </c>
-    </row>
-    <row r="26" spans="1:12">
+      <c r="L25" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="M25">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14">
       <c r="A26">
         <v>24</v>
       </c>
@@ -2208,8 +2457,14 @@
       <c r="K26">
         <v>18</v>
       </c>
-    </row>
-    <row r="27" spans="1:12" ht="37.5">
+      <c r="L26" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="M26">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" ht="37.5">
       <c r="A27">
         <v>25</v>
       </c>
@@ -2244,10 +2499,16 @@
         <v>32</v>
       </c>
       <c r="L27" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="M27">
+        <v>32</v>
+      </c>
+      <c r="N27" s="1" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="28" spans="1:12" ht="37.5">
+    <row r="28" spans="1:14" ht="37.5">
       <c r="A28">
         <v>26</v>
       </c>
@@ -2282,10 +2543,16 @@
         <v>32</v>
       </c>
       <c r="L28" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="M28">
+        <v>32</v>
+      </c>
+      <c r="N28" s="1" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="29" spans="1:12">
+    <row r="29" spans="1:14">
       <c r="A29">
         <v>27</v>
       </c>
@@ -2320,10 +2587,16 @@
         <v>14</v>
       </c>
       <c r="L29" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="M29">
+        <v>14</v>
+      </c>
+      <c r="N29" s="1" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="30" spans="1:12">
+    <row r="30" spans="1:14">
       <c r="A30">
         <v>28</v>
       </c>
@@ -2358,10 +2631,16 @@
         <v>14</v>
       </c>
       <c r="L30" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="M30">
+        <v>14</v>
+      </c>
+      <c r="N30" s="1" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="31" spans="1:12" ht="37.5">
+    <row r="31" spans="1:14" ht="37.5">
       <c r="A31">
         <v>29</v>
       </c>
@@ -2396,10 +2675,16 @@
         <v>12</v>
       </c>
       <c r="L31" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="M31">
+        <v>12</v>
+      </c>
+      <c r="N31" s="1" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="32" spans="1:12" ht="37.5">
+    <row r="32" spans="1:14">
       <c r="A32">
         <v>30</v>
       </c>
@@ -2434,10 +2719,16 @@
         <v>14</v>
       </c>
       <c r="L32" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="M32">
+        <v>14</v>
+      </c>
+      <c r="N32" s="1" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="33" spans="1:12" ht="75">
+    <row r="33" spans="1:14" ht="75">
       <c r="A33">
         <v>31</v>
       </c>
@@ -2472,10 +2763,16 @@
         <v>14</v>
       </c>
       <c r="L33" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="M33">
+        <v>14</v>
+      </c>
+      <c r="N33" s="1" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="34" spans="1:12" ht="56.25">
+    <row r="34" spans="1:14">
       <c r="A34">
         <v>32</v>
       </c>
@@ -2510,10 +2807,16 @@
         <v>14</v>
       </c>
       <c r="L34" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="M34">
+        <v>14</v>
+      </c>
+      <c r="N34" s="1" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="35" spans="1:12">
+    <row r="35" spans="1:14">
       <c r="A35">
         <v>33</v>
       </c>
@@ -2548,10 +2851,16 @@
         <v>14</v>
       </c>
       <c r="L35" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="M35">
+        <v>14</v>
+      </c>
+      <c r="N35" s="1" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="36" spans="1:12" ht="37.5">
+    <row r="36" spans="1:14">
       <c r="A36">
         <v>34</v>
       </c>
@@ -2586,10 +2895,16 @@
         <v>14</v>
       </c>
       <c r="L36" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="M36">
+        <v>14</v>
+      </c>
+      <c r="N36" s="1" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="37" spans="1:12" ht="37.5">
+    <row r="37" spans="1:14" ht="37.5">
       <c r="A37">
         <v>35</v>
       </c>
@@ -2624,10 +2939,16 @@
         <v>14</v>
       </c>
       <c r="L37" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="M37">
+        <v>14</v>
+      </c>
+      <c r="N37" s="1" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="38" spans="1:12" ht="93.75">
+    <row r="38" spans="1:14" ht="37.5">
       <c r="A38">
         <v>36</v>
       </c>
@@ -2662,10 +2983,16 @@
         <v>16</v>
       </c>
       <c r="L38" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="M38">
+        <v>16</v>
+      </c>
+      <c r="N38" s="1" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="39" spans="1:12">
+    <row r="39" spans="1:14">
       <c r="A39">
         <v>37</v>
       </c>
@@ -2699,8 +3026,14 @@
       <c r="K39">
         <v>14</v>
       </c>
-    </row>
-    <row r="40" spans="1:12">
+      <c r="L39" t="s">
+        <v>234</v>
+      </c>
+      <c r="M39">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14">
       <c r="A40">
         <v>38</v>
       </c>
@@ -2734,8 +3067,14 @@
       <c r="K40">
         <v>14</v>
       </c>
-    </row>
-    <row r="41" spans="1:12">
+      <c r="L40" t="s">
+        <v>235</v>
+      </c>
+      <c r="M40">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14">
       <c r="A41">
         <v>39</v>
       </c>
@@ -2769,8 +3108,14 @@
       <c r="K41">
         <v>14</v>
       </c>
-    </row>
-    <row r="42" spans="1:12" ht="37.5">
+      <c r="L41" t="s">
+        <v>236</v>
+      </c>
+      <c r="M41">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14" ht="37.5">
       <c r="A42">
         <v>40</v>
       </c>
@@ -2804,11 +3149,17 @@
       <c r="K42">
         <v>16</v>
       </c>
-      <c r="L42" s="1" t="s">
+      <c r="L42" t="s">
+        <v>214</v>
+      </c>
+      <c r="M42">
+        <v>16</v>
+      </c>
+      <c r="N42" s="1" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="43" spans="1:12">
+    <row r="43" spans="1:14">
       <c r="A43">
         <v>41</v>
       </c>
@@ -2842,11 +3193,17 @@
       <c r="K43">
         <v>14</v>
       </c>
-      <c r="L43" s="1" t="s">
+      <c r="L43" t="s">
+        <v>205</v>
+      </c>
+      <c r="M43">
+        <v>14</v>
+      </c>
+      <c r="N43" s="1" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="44" spans="1:12" ht="37.5">
+    <row r="44" spans="1:14">
       <c r="A44">
         <v>42</v>
       </c>
@@ -2881,10 +3238,16 @@
         <v>20</v>
       </c>
       <c r="L44" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="M44">
+        <v>20</v>
+      </c>
+      <c r="N44" s="1" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="45" spans="1:12" ht="93.75">
+    <row r="45" spans="1:14" ht="37.5">
       <c r="A45">
         <v>43</v>
       </c>
@@ -2918,8 +3281,14 @@
       <c r="K45">
         <v>10</v>
       </c>
-    </row>
-    <row r="46" spans="1:12" ht="93.75">
+      <c r="L45" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="M45">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14" ht="56.25">
       <c r="A46">
         <v>44</v>
       </c>
@@ -2953,8 +3322,14 @@
       <c r="K46">
         <v>10</v>
       </c>
-    </row>
-    <row r="47" spans="1:12" ht="37.5">
+      <c r="L46" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="M46">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14" ht="37.5">
       <c r="A47">
         <v>45</v>
       </c>
@@ -2989,10 +3364,16 @@
         <v>16</v>
       </c>
       <c r="L47" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="M47">
+        <v>16</v>
+      </c>
+      <c r="N47" s="1" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="48" spans="1:12" ht="37.5">
+    <row r="48" spans="1:14" ht="37.5">
       <c r="A48">
         <v>46</v>
       </c>
@@ -3027,10 +3408,16 @@
         <v>16</v>
       </c>
       <c r="L48" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="M48">
+        <v>16</v>
+      </c>
+      <c r="N48" s="1" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="49" spans="1:12" ht="37.5">
+    <row r="49" spans="1:14" ht="37.5">
       <c r="A49">
         <v>47</v>
       </c>
@@ -3065,10 +3452,16 @@
         <v>16</v>
       </c>
       <c r="L49" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="M49">
+        <v>16</v>
+      </c>
+      <c r="N49" s="1" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="50" spans="1:12" ht="37.5">
+    <row r="50" spans="1:14" ht="37.5">
       <c r="A50">
         <v>48</v>
       </c>
@@ -3103,10 +3496,16 @@
         <v>16</v>
       </c>
       <c r="L50" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="M50">
+        <v>16</v>
+      </c>
+      <c r="N50" s="1" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="51" spans="1:12">
+    <row r="51" spans="1:14">
       <c r="A51">
         <v>49</v>
       </c>
@@ -3140,8 +3539,14 @@
       <c r="K51" s="2">
         <v>10</v>
       </c>
-    </row>
-    <row r="52" spans="1:12">
+      <c r="L51" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="M51" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="52" spans="1:14">
       <c r="A52">
         <v>50</v>
       </c>
@@ -3175,8 +3580,14 @@
       <c r="K52" s="2">
         <v>10</v>
       </c>
-    </row>
-    <row r="53" spans="1:12">
+      <c r="L52" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="M52" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="53" spans="1:14">
       <c r="A53">
         <v>51</v>
       </c>
@@ -3210,19 +3621,52 @@
       <c r="K53">
         <v>14</v>
       </c>
-    </row>
-    <row r="54" spans="1:12">
+      <c r="L53" t="s">
+        <v>209</v>
+      </c>
+      <c r="M53">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="54" spans="1:14">
       <c r="A54">
         <v>52</v>
       </c>
       <c r="C54">
         <v>14</v>
       </c>
+      <c r="D54" s="1" t="s">
+        <v>240</v>
+      </c>
       <c r="E54">
         <v>14</v>
       </c>
-    </row>
-    <row r="55" spans="1:12">
+      <c r="F54" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="G54">
+        <v>14</v>
+      </c>
+      <c r="H54" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="I54">
+        <v>14</v>
+      </c>
+      <c r="J54" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="K54">
+        <v>14</v>
+      </c>
+      <c r="L54" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="M54">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="55" spans="1:14">
       <c r="A55">
         <v>53</v>
       </c>
@@ -3233,7 +3677,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="56" spans="1:12">
+    <row r="56" spans="1:14">
       <c r="A56">
         <v>54</v>
       </c>
@@ -3244,7 +3688,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="57" spans="1:12">
+    <row r="57" spans="1:14">
       <c r="A57">
         <v>55</v>
       </c>
@@ -3255,7 +3699,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="58" spans="1:12">
+    <row r="58" spans="1:14">
       <c r="A58">
         <v>56</v>
       </c>
@@ -3266,7 +3710,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="59" spans="1:12">
+    <row r="59" spans="1:14">
       <c r="A59">
         <v>57</v>
       </c>
@@ -3277,7 +3721,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="60" spans="1:12">
+    <row r="60" spans="1:14">
       <c r="A60">
         <v>58</v>
       </c>
@@ -3288,7 +3732,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="61" spans="1:12">
+    <row r="61" spans="1:14">
       <c r="A61">
         <v>59</v>
       </c>
@@ -3299,7 +3743,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="62" spans="1:12">
+    <row r="62" spans="1:14">
       <c r="A62">
         <v>60</v>
       </c>
@@ -3310,7 +3754,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="63" spans="1:12">
+    <row r="63" spans="1:14">
       <c r="A63">
         <v>61</v>
       </c>
@@ -3321,7 +3765,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="64" spans="1:12">
+    <row r="64" spans="1:14">
       <c r="A64">
         <v>62</v>
       </c>

--- a/Assets/Originals/Excels/Button/ButtonMessage.xlsx
+++ b/Assets/Originals/Excels/Button/ButtonMessage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\Button\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D5C5A2A-6CE7-4024-AC15-F28033AF30B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{696D8CCF-E623-4C3F-9E89-E730E78DBE3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="359" uniqueCount="241">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="237">
   <si>
     <t>number</t>
     <phoneticPr fontId="1"/>
@@ -668,9 +668,6 @@
   </si>
   <si>
     <t>靈敏度</t>
-  </si>
-  <si>
-    <t>音效</t>
   </si>
   <si>
     <t>畫面模式</t>
@@ -797,12 +794,6 @@
     <t>Sensibilidad</t>
   </si>
   <si>
-    <t>Música</t>
-  </si>
-  <si>
-    <t>Efectos</t>
-  </si>
-  <si>
     <t>Brillo</t>
   </si>
   <si>
@@ -914,9 +905,6 @@
     <t>Sensibilidade</t>
   </si>
   <si>
-    <t>Efeitos</t>
-  </si>
-  <si>
     <t>Brilho</t>
   </si>
   <si>
@@ -930,9 +918,6 @@
   </si>
   <si>
     <t>Resolução</t>
-  </si>
-  <si>
-    <t>Instruções de controle</t>
   </si>
   <si>
     <t>Descrição dos itens</t>
@@ -990,6 +975,10 @@
   </si>
   <si>
     <t>Portuguese</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Instruções de controle</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1391,22 +1380,22 @@
         <v>138</v>
       </c>
       <c r="H1" t="s">
+        <v>167</v>
+      </c>
+      <c r="I1" t="s">
         <v>168</v>
       </c>
-      <c r="I1" t="s">
-        <v>169</v>
-      </c>
       <c r="J1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="K1" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="L1" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="M1" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="N1" s="1" t="s">
         <v>51</v>
@@ -1441,13 +1430,13 @@
         <v>14</v>
       </c>
       <c r="J2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K2">
         <v>14</v>
       </c>
       <c r="L2" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="M2">
         <v>14</v>
@@ -1482,13 +1471,13 @@
         <v>14</v>
       </c>
       <c r="J3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K3">
         <v>14</v>
       </c>
       <c r="L3" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="M3">
         <v>14</v>
@@ -1526,13 +1515,13 @@
         <v>14</v>
       </c>
       <c r="J4" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="K4">
         <v>14</v>
       </c>
       <c r="L4" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="M4">
         <v>14</v>
@@ -1567,13 +1556,13 @@
         <v>24</v>
       </c>
       <c r="J5" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="K5">
         <v>24</v>
       </c>
       <c r="L5" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="M5">
         <v>24</v>
@@ -1611,16 +1600,16 @@
         <v>14</v>
       </c>
       <c r="J6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="K6">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L6" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="M6">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="N6" s="1" t="s">
         <v>53</v>
@@ -1648,20 +1637,20 @@
       <c r="G7" s="2">
         <v>14</v>
       </c>
-      <c r="H7" s="5" t="s">
-        <v>106</v>
+      <c r="H7" t="s">
+        <v>15</v>
       </c>
       <c r="I7" s="5">
         <v>14</v>
       </c>
       <c r="J7" t="s">
-        <v>178</v>
+        <v>15</v>
       </c>
       <c r="K7">
         <v>14</v>
       </c>
       <c r="L7" t="s">
-        <v>178</v>
+        <v>15</v>
       </c>
       <c r="M7">
         <v>14</v>
@@ -1689,20 +1678,20 @@
       <c r="G8" s="2">
         <v>14</v>
       </c>
-      <c r="H8" s="5" t="s">
-        <v>144</v>
+      <c r="H8" t="s">
+        <v>16</v>
       </c>
       <c r="I8" s="5">
         <v>14</v>
       </c>
       <c r="J8" t="s">
-        <v>179</v>
+        <v>16</v>
       </c>
       <c r="K8">
         <v>14</v>
       </c>
       <c r="L8" t="s">
-        <v>216</v>
+        <v>16</v>
       </c>
       <c r="M8">
         <v>14</v>
@@ -1737,13 +1726,13 @@
         <v>12</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="K9">
         <v>12</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="M9">
         <v>12</v>
@@ -1772,22 +1761,22 @@
         <v>10</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I10" s="5">
         <v>10</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="K10">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="M10">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:14">
@@ -1819,16 +1808,16 @@
         <v>16</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="K11">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="M11">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -1854,19 +1843,19 @@
         <v>16</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I12" s="5">
         <v>16</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="K12">
         <v>16</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="M12">
         <v>16</v>
@@ -1895,19 +1884,19 @@
         <v>10</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I13" s="5">
         <v>10</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="K13">
         <v>10</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="M13">
         <v>10</v>
@@ -1936,19 +1925,19 @@
         <v>10</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="I14" s="5">
         <v>10</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="K14">
         <v>8</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>222</v>
+        <v>236</v>
       </c>
       <c r="M14">
         <v>8</v>
@@ -1980,22 +1969,22 @@
         <v>16</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="I15" s="5">
         <v>16</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="K15">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="M15">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="N15" s="1" t="s">
         <v>94</v>
@@ -2024,22 +2013,22 @@
         <v>16</v>
       </c>
       <c r="H16" s="5" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I16" s="5">
         <v>16</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="K16">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="M16">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="N16" s="1" t="s">
         <v>94</v>
@@ -2068,22 +2057,22 @@
         <v>10</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="I17" s="5">
         <v>10</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="K17">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="M17">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18" spans="1:14" ht="37.5">
@@ -2109,22 +2098,22 @@
         <v>10</v>
       </c>
       <c r="H18" s="5" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="I18" s="5">
         <v>10</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="K18">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="M18">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -2238,13 +2227,13 @@
         <v>24</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="K21">
         <v>18</v>
       </c>
       <c r="L21" s="1" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="M21">
         <v>18</v>
@@ -2276,22 +2265,22 @@
         <v>24</v>
       </c>
       <c r="H22" s="5" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="I22" s="5">
         <v>24</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="K22">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="M22">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="N22" s="1" t="s">
         <v>56</v>
@@ -2326,13 +2315,13 @@
         <v>24</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="K23">
         <v>18</v>
       </c>
       <c r="L23" s="1" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="M23">
         <v>18</v>
@@ -2364,19 +2353,19 @@
         <v>24</v>
       </c>
       <c r="H24" s="5" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="I24" s="5">
         <v>24</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="K24">
         <v>18</v>
       </c>
       <c r="L24" s="1" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="M24">
         <v>18</v>
@@ -2405,19 +2394,19 @@
         <v>24</v>
       </c>
       <c r="H25" s="5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="I25" s="5">
         <v>24</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="K25">
         <v>18</v>
       </c>
       <c r="L25" s="1" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="M25">
         <v>18</v>
@@ -2446,19 +2435,19 @@
         <v>24</v>
       </c>
       <c r="H26" s="5" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="I26" s="5">
         <v>24</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="K26">
         <v>18</v>
       </c>
       <c r="L26" s="1" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="M26">
         <v>18</v>
@@ -2493,13 +2482,13 @@
         <v>32</v>
       </c>
       <c r="J27" s="1" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="K27">
         <v>32</v>
       </c>
       <c r="L27" s="1" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="M27">
         <v>32</v>
@@ -2537,13 +2526,13 @@
         <v>32</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="K28">
         <v>32</v>
       </c>
       <c r="L28" s="1" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="M28">
         <v>32</v>
@@ -2581,13 +2570,13 @@
         <v>14</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="K29">
         <v>14</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="M29">
         <v>14</v>
@@ -2625,13 +2614,13 @@
         <v>14</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="K30">
         <v>14</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="M30">
         <v>14</v>
@@ -2669,13 +2658,13 @@
         <v>12</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="K31">
         <v>12</v>
       </c>
       <c r="L31" s="1" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="M31">
         <v>12</v>
@@ -2707,19 +2696,19 @@
         <v>14</v>
       </c>
       <c r="H32" s="5" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="I32" s="5">
         <v>14</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="K32">
         <v>14</v>
       </c>
       <c r="L32" s="1" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="M32">
         <v>14</v>
@@ -2757,13 +2746,13 @@
         <v>14</v>
       </c>
       <c r="J33" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="K33">
         <v>14</v>
       </c>
       <c r="L33" s="1" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="M33">
         <v>14</v>
@@ -2801,13 +2790,13 @@
         <v>14</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="K34">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L34" s="1" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="M34">
         <v>14</v>
@@ -2839,19 +2828,19 @@
         <v>14</v>
       </c>
       <c r="H35" s="5" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I35" s="5">
         <v>14</v>
       </c>
       <c r="J35" s="1" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="K35">
         <v>14</v>
       </c>
       <c r="L35" s="1" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="M35">
         <v>14</v>
@@ -2883,22 +2872,22 @@
         <v>14</v>
       </c>
       <c r="H36" s="5" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="I36" s="5">
         <v>14</v>
       </c>
       <c r="J36" s="1" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="K36">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L36" s="1" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="M36">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="N36" s="1" t="s">
         <v>68</v>
@@ -2927,19 +2916,19 @@
         <v>14</v>
       </c>
       <c r="H37" s="5" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="I37" s="5">
         <v>14</v>
       </c>
       <c r="J37" s="1" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="K37">
         <v>14</v>
       </c>
       <c r="L37" s="1" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="M37">
         <v>14</v>
@@ -2971,22 +2960,22 @@
         <v>20</v>
       </c>
       <c r="H38" s="5" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="I38" s="5">
         <v>20</v>
       </c>
       <c r="J38" s="1" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="K38">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="L38" s="1" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="M38">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="N38" s="1" t="s">
         <v>91</v>
@@ -3015,19 +3004,19 @@
         <v>14</v>
       </c>
       <c r="H39" s="5" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I39" s="5">
         <v>14</v>
       </c>
       <c r="J39" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="K39">
         <v>14</v>
       </c>
       <c r="L39" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="M39">
         <v>14</v>
@@ -3056,19 +3045,19 @@
         <v>14</v>
       </c>
       <c r="H40" s="5" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I40" s="5">
         <v>14</v>
       </c>
       <c r="J40" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="K40">
         <v>14</v>
       </c>
       <c r="L40" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="M40">
         <v>14</v>
@@ -3097,19 +3086,19 @@
         <v>14</v>
       </c>
       <c r="H41" s="5" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="I41" s="5">
         <v>14</v>
       </c>
       <c r="J41" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="K41">
         <v>14</v>
       </c>
       <c r="L41" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="M41">
         <v>14</v>
@@ -3144,13 +3133,13 @@
         <v>20</v>
       </c>
       <c r="J42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="K42">
         <v>16</v>
       </c>
       <c r="L42" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="M42">
         <v>16</v>
@@ -3182,19 +3171,19 @@
         <v>14</v>
       </c>
       <c r="H43" s="5" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="I43" s="5">
         <v>14</v>
       </c>
       <c r="J43" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="K43">
         <v>14</v>
       </c>
       <c r="L43" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="M43">
         <v>14</v>
@@ -3226,19 +3215,19 @@
         <v>20</v>
       </c>
       <c r="H44" s="5" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="I44" s="5">
         <v>20</v>
       </c>
       <c r="J44" s="1" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="K44">
         <v>20</v>
       </c>
       <c r="L44" s="1" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="M44">
         <v>20</v>
@@ -3270,22 +3259,22 @@
         <v>10</v>
       </c>
       <c r="H45" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="I45" s="5">
         <v>10</v>
       </c>
       <c r="J45" s="1" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="K45">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L45" s="1" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="M45">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="46" spans="1:14" ht="56.25">
@@ -3311,22 +3300,22 @@
         <v>10</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="I46" s="5">
         <v>10</v>
       </c>
       <c r="J46" s="1" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="K46">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L46" s="1" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="M46">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="47" spans="1:14" ht="37.5">
@@ -3352,19 +3341,19 @@
         <v>16</v>
       </c>
       <c r="H47" s="5" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="I47" s="5">
         <v>16</v>
       </c>
       <c r="J47" s="1" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="K47">
         <v>16</v>
       </c>
       <c r="L47" s="1" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="M47">
         <v>16</v>
@@ -3396,19 +3385,19 @@
         <v>16</v>
       </c>
       <c r="H48" s="5" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I48" s="5">
         <v>16</v>
       </c>
       <c r="J48" s="1" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="K48">
         <v>16</v>
       </c>
       <c r="L48" s="1" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="M48">
         <v>16</v>
@@ -3440,22 +3429,22 @@
         <v>16</v>
       </c>
       <c r="H49" s="5" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="I49" s="5">
         <v>16</v>
       </c>
       <c r="J49" s="1" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="K49">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L49" s="1" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="M49">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="N49" s="1" t="s">
         <v>96</v>
@@ -3484,22 +3473,22 @@
         <v>16</v>
       </c>
       <c r="H50" s="5" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I50" s="5">
         <v>16</v>
       </c>
       <c r="J50" s="1" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="K50">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L50" s="1" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="M50">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="N50" s="1" t="s">
         <v>96</v>
@@ -3513,37 +3502,37 @@
         <v>139</v>
       </c>
       <c r="C51">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D51" s="1" t="s">
         <v>139</v>
       </c>
       <c r="E51">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F51" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="G51" s="2">
-        <v>10</v>
+      <c r="G51">
+        <v>14</v>
       </c>
       <c r="H51" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="I51" s="2">
-        <v>10</v>
+      <c r="I51">
+        <v>14</v>
       </c>
       <c r="J51" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="K51" s="2">
-        <v>10</v>
+      <c r="K51">
+        <v>14</v>
       </c>
       <c r="L51" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="M51" s="2">
-        <v>10</v>
+      <c r="M51">
+        <v>14</v>
       </c>
     </row>
     <row r="52" spans="1:14">
@@ -3551,40 +3540,40 @@
         <v>50</v>
       </c>
       <c r="B52" t="s">
+        <v>169</v>
+      </c>
+      <c r="C52">
+        <v>14</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="E52">
+        <v>14</v>
+      </c>
+      <c r="F52" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="G52">
+        <v>14</v>
+      </c>
+      <c r="H52" s="5" t="s">
         <v>170</v>
       </c>
-      <c r="C52">
-        <v>10</v>
-      </c>
-      <c r="D52" s="1" t="s">
+      <c r="I52">
+        <v>14</v>
+      </c>
+      <c r="J52" s="5" t="s">
         <v>170</v>
       </c>
-      <c r="E52">
-        <v>10</v>
-      </c>
-      <c r="F52" s="2" t="s">
+      <c r="K52">
+        <v>14</v>
+      </c>
+      <c r="L52" s="5" t="s">
         <v>170</v>
       </c>
-      <c r="G52">
-        <v>10</v>
-      </c>
-      <c r="H52" s="5" t="s">
-        <v>171</v>
-      </c>
-      <c r="I52">
-        <v>10</v>
-      </c>
-      <c r="J52" s="5" t="s">
-        <v>171</v>
-      </c>
-      <c r="K52" s="2">
-        <v>10</v>
-      </c>
-      <c r="L52" s="5" t="s">
-        <v>171</v>
-      </c>
-      <c r="M52" s="2">
-        <v>10</v>
+      <c r="M52">
+        <v>14</v>
       </c>
     </row>
     <row r="53" spans="1:14">
@@ -3592,37 +3581,37 @@
         <v>51</v>
       </c>
       <c r="B53" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="C53">
         <v>14</v>
       </c>
       <c r="D53" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="E53">
         <v>14</v>
       </c>
       <c r="F53" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="G53">
         <v>14</v>
       </c>
       <c r="H53" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="I53">
         <v>14</v>
       </c>
       <c r="J53" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="K53">
         <v>14</v>
       </c>
       <c r="L53" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="M53">
         <v>14</v>
@@ -3632,35 +3621,38 @@
       <c r="A54">
         <v>52</v>
       </c>
+      <c r="B54" s="1" t="s">
+        <v>235</v>
+      </c>
       <c r="C54">
         <v>14</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="E54">
         <v>14</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="G54">
         <v>14</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="I54">
         <v>14</v>
       </c>
       <c r="J54" s="1" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="K54">
         <v>14</v>
       </c>
       <c r="L54" s="1" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="M54">
         <v>14</v>

--- a/Assets/Originals/Excels/Button/ButtonMessage.xlsx
+++ b/Assets/Originals/Excels/Button/ButtonMessage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\Button\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{696D8CCF-E623-4C3F-9E89-E730E78DBE3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C292811D-2BA6-4082-84F2-F1450B65B42F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -824,9 +824,6 @@
     <t>Descripción de la brújula</t>
   </si>
   <si>
-    <t>Ajuste de volumen</t>
-  </si>
-  <si>
     <t>Pantalla</t>
   </si>
   <si>
@@ -926,9 +923,6 @@
     <t>Descrição da bússola</t>
   </si>
   <si>
-    <t>Ajuste de volume</t>
-  </si>
-  <si>
     <t>Tela</t>
   </si>
   <si>
@@ -979,6 +973,14 @@
   </si>
   <si>
     <t>Instruções de controle</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>volumen</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>volume</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1389,13 +1391,13 @@
         <v>171</v>
       </c>
       <c r="K1" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="L1" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="M1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="N1" s="1" t="s">
         <v>51</v>
@@ -1436,7 +1438,7 @@
         <v>14</v>
       </c>
       <c r="L2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="M2">
         <v>14</v>
@@ -1477,7 +1479,7 @@
         <v>14</v>
       </c>
       <c r="L3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="M3">
         <v>14</v>
@@ -1521,7 +1523,7 @@
         <v>14</v>
       </c>
       <c r="L4" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="M4">
         <v>14</v>
@@ -1562,7 +1564,7 @@
         <v>24</v>
       </c>
       <c r="L5" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="M5">
         <v>24</v>
@@ -1606,7 +1608,7 @@
         <v>12</v>
       </c>
       <c r="L6" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="M6">
         <v>12</v>
@@ -1732,7 +1734,7 @@
         <v>12</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="M9">
         <v>12</v>
@@ -1773,7 +1775,7 @@
         <v>8</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="M10">
         <v>8</v>
@@ -1814,7 +1816,7 @@
         <v>12</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="M11">
         <v>12</v>
@@ -1855,7 +1857,7 @@
         <v>16</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="M12">
         <v>16</v>
@@ -1896,7 +1898,7 @@
         <v>10</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="M13">
         <v>10</v>
@@ -1937,7 +1939,7 @@
         <v>8</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="M14">
         <v>8</v>
@@ -2069,7 +2071,7 @@
         <v>8</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="M17">
         <v>8</v>
@@ -2110,7 +2112,7 @@
         <v>6</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="M18">
         <v>6</v>
@@ -2233,7 +2235,7 @@
         <v>18</v>
       </c>
       <c r="L21" s="1" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="M21">
         <v>18</v>
@@ -2271,16 +2273,16 @@
         <v>24</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>187</v>
+        <v>235</v>
       </c>
       <c r="K22">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>220</v>
+        <v>236</v>
       </c>
       <c r="M22">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="N22" s="1" t="s">
         <v>56</v>
@@ -2321,7 +2323,7 @@
         <v>18</v>
       </c>
       <c r="L23" s="1" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="M23">
         <v>18</v>
@@ -2359,13 +2361,13 @@
         <v>24</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="K24">
         <v>18</v>
       </c>
       <c r="L24" s="1" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="M24">
         <v>18</v>
@@ -2400,13 +2402,13 @@
         <v>24</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="K25">
         <v>18</v>
       </c>
       <c r="L25" s="1" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="M25">
         <v>18</v>
@@ -2441,13 +2443,13 @@
         <v>24</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="K26">
         <v>18</v>
       </c>
       <c r="L26" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="M26">
         <v>18</v>
@@ -2482,13 +2484,13 @@
         <v>32</v>
       </c>
       <c r="J27" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="K27">
         <v>32</v>
       </c>
       <c r="L27" s="1" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="M27">
         <v>32</v>
@@ -2526,13 +2528,13 @@
         <v>32</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="K28">
         <v>32</v>
       </c>
       <c r="L28" s="1" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="M28">
         <v>32</v>
@@ -2570,13 +2572,13 @@
         <v>14</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="K29">
         <v>14</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="M29">
         <v>14</v>
@@ -2614,13 +2616,13 @@
         <v>14</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="K30">
         <v>14</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="M30">
         <v>14</v>
@@ -2664,7 +2666,7 @@
         <v>12</v>
       </c>
       <c r="L31" s="1" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="M31">
         <v>12</v>
@@ -2702,13 +2704,13 @@
         <v>14</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="K32">
         <v>14</v>
       </c>
       <c r="L32" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="M32">
         <v>14</v>
@@ -2752,7 +2754,7 @@
         <v>14</v>
       </c>
       <c r="L33" s="1" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="M33">
         <v>14</v>
@@ -2790,13 +2792,13 @@
         <v>14</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="K34">
         <v>12</v>
       </c>
       <c r="L34" s="1" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="M34">
         <v>14</v>
@@ -2834,13 +2836,13 @@
         <v>14</v>
       </c>
       <c r="J35" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="K35">
         <v>14</v>
       </c>
       <c r="L35" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="M35">
         <v>14</v>
@@ -2878,13 +2880,13 @@
         <v>14</v>
       </c>
       <c r="J36" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="K36">
         <v>12</v>
       </c>
       <c r="L36" s="1" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="M36">
         <v>12</v>
@@ -2922,13 +2924,13 @@
         <v>14</v>
       </c>
       <c r="J37" s="1" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="K37">
         <v>14</v>
       </c>
       <c r="L37" s="1" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="M37">
         <v>14</v>
@@ -2966,13 +2968,13 @@
         <v>20</v>
       </c>
       <c r="J38" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="K38">
         <v>12</v>
       </c>
       <c r="L38" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="M38">
         <v>12</v>
@@ -3010,13 +3012,13 @@
         <v>14</v>
       </c>
       <c r="J39" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="K39">
         <v>14</v>
       </c>
       <c r="L39" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="M39">
         <v>14</v>
@@ -3051,13 +3053,13 @@
         <v>14</v>
       </c>
       <c r="J40" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="K40">
         <v>14</v>
       </c>
       <c r="L40" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="M40">
         <v>14</v>
@@ -3092,13 +3094,13 @@
         <v>14</v>
       </c>
       <c r="J41" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="K41">
         <v>14</v>
       </c>
       <c r="L41" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="M41">
         <v>14</v>
@@ -3139,7 +3141,7 @@
         <v>16</v>
       </c>
       <c r="L42" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="M42">
         <v>16</v>
@@ -3177,13 +3179,13 @@
         <v>14</v>
       </c>
       <c r="J43" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="K43">
         <v>14</v>
       </c>
       <c r="L43" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="M43">
         <v>14</v>
@@ -3221,13 +3223,13 @@
         <v>20</v>
       </c>
       <c r="J44" s="1" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="K44">
         <v>20</v>
       </c>
       <c r="L44" s="1" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="M44">
         <v>20</v>
@@ -3265,13 +3267,13 @@
         <v>10</v>
       </c>
       <c r="J45" s="1" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="K45">
         <v>8</v>
       </c>
       <c r="L45" s="1" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="M45">
         <v>8</v>
@@ -3306,13 +3308,13 @@
         <v>10</v>
       </c>
       <c r="J46" s="1" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="K46">
         <v>8</v>
       </c>
       <c r="L46" s="1" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="M46">
         <v>8</v>
@@ -3581,37 +3583,37 @@
         <v>51</v>
       </c>
       <c r="B53" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C53">
         <v>14</v>
       </c>
       <c r="D53" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E53">
         <v>14</v>
       </c>
       <c r="F53" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="G53">
         <v>14</v>
       </c>
       <c r="H53" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="I53">
         <v>14</v>
       </c>
       <c r="J53" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="K53">
         <v>14</v>
       </c>
       <c r="L53" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="M53">
         <v>14</v>
@@ -3622,37 +3624,37 @@
         <v>52</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C54">
         <v>14</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E54">
         <v>14</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="G54">
         <v>14</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="I54">
         <v>14</v>
       </c>
       <c r="J54" s="1" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="K54">
         <v>14</v>
       </c>
       <c r="L54" s="1" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="M54">
         <v>14</v>

--- a/Assets/Originals/Excels/Button/ButtonMessage.xlsx
+++ b/Assets/Originals/Excels/Button/ButtonMessage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\Button\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C292811D-2BA6-4082-84F2-F1450B65B42F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10A24046-AF61-44B1-A515-9FDE63045223}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="237">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="236">
   <si>
     <t>number</t>
     <phoneticPr fontId="1"/>
@@ -174,17 +174,6 @@
   </si>
   <si>
     <t>コンパス説明</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>日本語</t>
-    <rPh sb="0" eb="3">
-      <t>ニホンゴ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>日本語</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -584,9 +573,6 @@
     <t>罗盘说明</t>
   </si>
   <si>
-    <t>日本語</t>
-  </si>
-  <si>
     <t>English</t>
   </si>
   <si>
@@ -749,33 +735,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>繁体中国語</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <r>
-      <t>繁体中</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Yu Gothic"/>
-        <family val="2"/>
-      </rPr>
-      <t>国</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Microsoft JhengHei"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>語</t>
-    </r>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>messageSpanish</t>
   </si>
   <si>
@@ -981,6 +940,25 @@
   </si>
   <si>
     <t>volume</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>简体中文</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>繁體中文</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>日本</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>日本</t>
+    <rPh sb="0" eb="2">
+      <t>ニホン</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1023,8 +1001,10 @@
     </font>
     <font>
       <sz val="11"/>
-      <name val="Yu Gothic"/>
+      <color theme="1"/>
+      <name val="Microsoft YaHei"/>
       <family val="2"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1047,7 +1027,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1059,6 +1039,9 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1376,31 +1359,31 @@
         <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="G1" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="H1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="I1" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="J1" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="K1" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="L1" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="M1" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="2" spans="1:14">
@@ -1420,25 +1403,25 @@
         <v>14</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="G2" s="2">
         <v>14</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="I2" s="5">
         <v>14</v>
       </c>
       <c r="J2" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="K2">
         <v>14</v>
       </c>
       <c r="L2" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="M2">
         <v>14</v>
@@ -1461,31 +1444,31 @@
         <v>14</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="G3" s="2">
         <v>14</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="I3" s="5">
         <v>14</v>
       </c>
       <c r="J3" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="K3">
         <v>14</v>
       </c>
       <c r="L3" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="M3">
         <v>14</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -1505,25 +1488,25 @@
         <v>14</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="G4" s="2">
         <v>14</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="I4" s="5">
         <v>14</v>
       </c>
       <c r="J4" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="K4">
         <v>14</v>
       </c>
       <c r="L4" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="M4">
         <v>14</v>
@@ -1546,31 +1529,31 @@
         <v>24</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="G5" s="2">
         <v>24</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="I5" s="5">
         <v>24</v>
       </c>
       <c r="J5" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="K5">
         <v>24</v>
       </c>
       <c r="L5" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="M5">
         <v>24</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6" spans="1:14">
@@ -1590,31 +1573,31 @@
         <v>14</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="G6" s="2">
         <v>14</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="I6" s="5">
         <v>14</v>
       </c>
       <c r="J6" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="K6">
         <v>12</v>
       </c>
       <c r="L6" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="M6">
         <v>12</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -1634,7 +1617,7 @@
         <v>14</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="G7" s="2">
         <v>14</v>
@@ -1704,37 +1687,37 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C9">
         <v>12</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E9">
         <v>12</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="G9" s="2">
         <v>12</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="I9" s="5">
         <v>12</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="K9">
         <v>12</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="M9">
         <v>12</v>
@@ -1757,25 +1740,25 @@
         <v>10</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="G10" s="2">
         <v>10</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="I10" s="5">
         <v>10</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="K10">
         <v>8</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="M10">
         <v>8</v>
@@ -1792,31 +1775,31 @@
         <v>16</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E11">
         <v>16</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="G11" s="2">
         <v>16</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="I11" s="5">
         <v>16</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="K11">
         <v>12</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="M11">
         <v>12</v>
@@ -1839,25 +1822,25 @@
         <v>16</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="G12" s="2">
         <v>16</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="I12" s="5">
         <v>16</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="K12">
         <v>16</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="M12">
         <v>16</v>
@@ -1880,25 +1863,25 @@
         <v>10</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="G13" s="2">
         <v>10</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="I13" s="5">
         <v>10</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="K13">
         <v>10</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="M13">
         <v>10</v>
@@ -1921,31 +1904,31 @@
         <v>8</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G14" s="2">
         <v>10</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="I14" s="5">
         <v>10</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="K14">
         <v>8</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="M14">
         <v>8</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="37.5">
@@ -1965,31 +1948,31 @@
         <v>16</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G15" s="2">
         <v>16</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="I15" s="5">
         <v>16</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="K15">
         <v>14</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="M15">
         <v>14</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="37.5">
@@ -2009,31 +1992,31 @@
         <v>16</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G16" s="2">
         <v>16</v>
       </c>
       <c r="H16" s="5" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="I16" s="5">
         <v>16</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="K16">
         <v>14</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="M16">
         <v>14</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17" spans="1:14" ht="37.5">
@@ -2053,25 +2036,25 @@
         <v>10</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G17" s="2">
         <v>10</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="I17" s="5">
         <v>10</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="K17">
         <v>8</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="M17">
         <v>8</v>
@@ -2088,31 +2071,31 @@
         <v>10</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E18">
         <v>8</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="G18" s="2">
         <v>10</v>
       </c>
       <c r="H18" s="5" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="I18" s="5">
         <v>10</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="K18">
         <v>6</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="M18">
         <v>6</v>
@@ -2123,37 +2106,37 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>33</v>
+        <v>235</v>
       </c>
       <c r="C19">
         <v>16</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>34</v>
+        <v>234</v>
       </c>
       <c r="E19">
         <v>16</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>117</v>
+        <v>234</v>
       </c>
       <c r="G19" s="2">
         <v>16</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>117</v>
+        <v>234</v>
       </c>
       <c r="I19" s="5">
         <v>16</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>117</v>
+        <v>234</v>
       </c>
       <c r="K19">
         <v>16</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>117</v>
+        <v>234</v>
       </c>
       <c r="M19">
         <v>16</v>
@@ -2164,37 +2147,37 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C20">
         <v>16</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E20">
         <v>16</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="G20" s="2">
         <v>16</v>
       </c>
       <c r="H20" s="5" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="I20" s="5">
         <v>16</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="K20">
         <v>16</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="M20">
         <v>16</v>
@@ -2205,7 +2188,7 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C21">
         <v>24</v>
@@ -2217,31 +2200,31 @@
         <v>18</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="G21" s="2">
         <v>24</v>
       </c>
       <c r="H21" s="5" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="I21" s="5">
         <v>24</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="K21">
         <v>18</v>
       </c>
       <c r="L21" s="1" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="M21">
         <v>18</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -2249,43 +2232,43 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C22">
         <v>24</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E22">
         <v>18</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="G22" s="2">
         <v>24</v>
       </c>
       <c r="H22" s="5" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="I22" s="5">
         <v>24</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="K22">
         <v>18</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="M22">
         <v>18</v>
       </c>
       <c r="N22" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="23" spans="1:14">
@@ -2293,43 +2276,43 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C23">
         <v>24</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E23">
         <v>18</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="G23" s="2">
         <v>24</v>
       </c>
       <c r="H23" s="5" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="I23" s="5">
         <v>24</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="K23">
         <v>18</v>
       </c>
       <c r="L23" s="1" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="M23">
         <v>18</v>
       </c>
       <c r="N23" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="24" spans="1:14">
@@ -2337,37 +2320,37 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C24">
         <v>24</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E24">
         <v>18</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="G24" s="2">
         <v>24</v>
       </c>
       <c r="H24" s="5" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="I24" s="5">
         <v>24</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="K24">
         <v>18</v>
       </c>
       <c r="L24" s="1" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="M24">
         <v>18</v>
@@ -2378,37 +2361,37 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C25">
         <v>24</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E25">
         <v>18</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="G25" s="2">
         <v>24</v>
       </c>
       <c r="H25" s="5" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="I25" s="5">
         <v>24</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="K25">
         <v>18</v>
       </c>
       <c r="L25" s="1" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="M25">
         <v>18</v>
@@ -2419,37 +2402,37 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C26">
         <v>24</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E26">
         <v>18</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="G26" s="2">
         <v>24</v>
       </c>
       <c r="H26" s="5" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="I26" s="5">
         <v>24</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="K26">
         <v>18</v>
       </c>
       <c r="L26" s="1" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="M26">
         <v>18</v>
@@ -2460,43 +2443,43 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C27">
         <v>32</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E27">
         <v>32</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="G27" s="2">
         <v>32</v>
       </c>
       <c r="H27" s="5" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="I27" s="5">
         <v>32</v>
       </c>
       <c r="J27" s="1" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="K27">
         <v>32</v>
       </c>
       <c r="L27" s="1" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="M27">
         <v>32</v>
       </c>
       <c r="N27" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="28" spans="1:14" ht="37.5">
@@ -2504,43 +2487,43 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C28">
         <v>32</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E28">
         <v>32</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="G28" s="2">
         <v>32</v>
       </c>
       <c r="H28" s="5" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="I28" s="5">
         <v>32</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="K28">
         <v>32</v>
       </c>
       <c r="L28" s="1" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="M28">
         <v>32</v>
       </c>
       <c r="N28" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="29" spans="1:14">
@@ -2548,43 +2531,43 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
+        <v>45</v>
+      </c>
+      <c r="C29">
+        <v>14</v>
+      </c>
+      <c r="D29" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="C29">
-        <v>14</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>49</v>
-      </c>
       <c r="E29">
         <v>14</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="G29" s="2">
         <v>14</v>
       </c>
       <c r="H29" s="5" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="I29" s="5">
         <v>14</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="K29">
         <v>14</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="M29">
         <v>14</v>
       </c>
       <c r="N29" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -2592,43 +2575,43 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
+        <v>46</v>
+      </c>
+      <c r="C30">
+        <v>14</v>
+      </c>
+      <c r="D30" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="C30">
-        <v>14</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>50</v>
-      </c>
       <c r="E30">
         <v>14</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="G30" s="2">
         <v>14</v>
       </c>
       <c r="H30" s="5" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="I30" s="5">
         <v>14</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="K30">
         <v>14</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="M30">
         <v>14</v>
       </c>
       <c r="N30" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="31" spans="1:14" ht="37.5">
@@ -2636,43 +2619,43 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C31">
         <v>12</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E31">
         <v>12</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="G31" s="2">
         <v>12</v>
       </c>
       <c r="H31" s="5" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="I31" s="5">
         <v>12</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="K31">
         <v>12</v>
       </c>
       <c r="L31" s="1" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="M31">
         <v>12</v>
       </c>
       <c r="N31" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="32" spans="1:14">
@@ -2680,43 +2663,43 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
+        <v>59</v>
+      </c>
+      <c r="C32">
+        <v>14</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E32">
+        <v>14</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="G32" s="2">
+        <v>14</v>
+      </c>
+      <c r="H32" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="I32" s="5">
+        <v>14</v>
+      </c>
+      <c r="J32" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="K32">
+        <v>14</v>
+      </c>
+      <c r="L32" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="M32">
+        <v>14</v>
+      </c>
+      <c r="N32" s="1" t="s">
         <v>61</v>
-      </c>
-      <c r="C32">
-        <v>14</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="E32">
-        <v>14</v>
-      </c>
-      <c r="F32" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="G32" s="2">
-        <v>14</v>
-      </c>
-      <c r="H32" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="I32" s="5">
-        <v>14</v>
-      </c>
-      <c r="J32" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="K32">
-        <v>14</v>
-      </c>
-      <c r="L32" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="M32">
-        <v>14</v>
-      </c>
-      <c r="N32" s="1" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="33" spans="1:14" ht="75">
@@ -2736,31 +2719,31 @@
         <v>14</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="G33" s="2">
         <v>14</v>
       </c>
       <c r="H33" s="5" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="I33" s="5">
         <v>14</v>
       </c>
       <c r="J33" s="1" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="K33">
         <v>14</v>
       </c>
       <c r="L33" s="1" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="M33">
         <v>14</v>
       </c>
       <c r="N33" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="34" spans="1:14">
@@ -2768,43 +2751,43 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C34">
         <v>14</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E34">
         <v>14</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="G34" s="2">
         <v>14</v>
       </c>
       <c r="H34" s="5" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="I34" s="5">
         <v>14</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="K34">
         <v>12</v>
       </c>
       <c r="L34" s="1" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="M34">
         <v>14</v>
       </c>
       <c r="N34" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="35" spans="1:14">
@@ -2812,43 +2795,43 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
+        <v>64</v>
+      </c>
+      <c r="C35">
+        <v>14</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E35">
+        <v>14</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="G35" s="2">
+        <v>14</v>
+      </c>
+      <c r="H35" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="I35" s="5">
+        <v>14</v>
+      </c>
+      <c r="J35" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="K35">
+        <v>14</v>
+      </c>
+      <c r="L35" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="M35">
+        <v>14</v>
+      </c>
+      <c r="N35" s="1" t="s">
         <v>66</v>
-      </c>
-      <c r="C35">
-        <v>14</v>
-      </c>
-      <c r="D35" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="E35">
-        <v>14</v>
-      </c>
-      <c r="F35" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="G35" s="2">
-        <v>14</v>
-      </c>
-      <c r="H35" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="I35" s="5">
-        <v>14</v>
-      </c>
-      <c r="J35" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="K35">
-        <v>14</v>
-      </c>
-      <c r="L35" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="M35">
-        <v>14</v>
-      </c>
-      <c r="N35" s="1" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="36" spans="1:14">
@@ -2856,43 +2839,43 @@
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C36">
         <v>14</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E36">
         <v>14</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="G36" s="2">
         <v>14</v>
       </c>
       <c r="H36" s="5" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="I36" s="5">
         <v>14</v>
       </c>
       <c r="J36" s="1" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="K36">
         <v>12</v>
       </c>
       <c r="L36" s="1" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="M36">
         <v>12</v>
       </c>
       <c r="N36" s="1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="37" spans="1:14" ht="37.5">
@@ -2900,43 +2883,43 @@
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C37">
         <v>14</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E37">
         <v>14</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="G37" s="2">
         <v>14</v>
       </c>
       <c r="H37" s="5" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="I37" s="5">
         <v>14</v>
       </c>
       <c r="J37" s="1" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="K37">
         <v>14</v>
       </c>
       <c r="L37" s="1" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="M37">
         <v>14</v>
       </c>
       <c r="N37" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="38" spans="1:14" ht="37.5">
@@ -2944,43 +2927,43 @@
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C38">
         <v>20</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E38">
         <v>16</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="G38" s="2">
         <v>20</v>
       </c>
       <c r="H38" s="5" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="I38" s="5">
         <v>20</v>
       </c>
       <c r="J38" s="1" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="K38">
         <v>12</v>
       </c>
       <c r="L38" s="1" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="M38">
         <v>12</v>
       </c>
       <c r="N38" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="39" spans="1:14">
@@ -2988,37 +2971,37 @@
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C39">
         <v>14</v>
       </c>
       <c r="D39" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E39">
         <v>14</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="G39" s="2">
         <v>14</v>
       </c>
       <c r="H39" s="5" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="I39" s="5">
         <v>14</v>
       </c>
       <c r="J39" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="K39">
         <v>14</v>
       </c>
       <c r="L39" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="M39">
         <v>14</v>
@@ -3029,37 +3012,37 @@
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C40">
         <v>14</v>
       </c>
       <c r="D40" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E40">
         <v>14</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="G40" s="2">
         <v>14</v>
       </c>
       <c r="H40" s="5" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="I40" s="5">
         <v>14</v>
       </c>
       <c r="J40" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="K40">
         <v>14</v>
       </c>
       <c r="L40" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="M40">
         <v>14</v>
@@ -3070,37 +3053,37 @@
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C41">
         <v>14</v>
       </c>
       <c r="D41" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E41">
         <v>14</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="G41" s="2">
         <v>14</v>
       </c>
       <c r="H41" s="5" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="I41" s="5">
         <v>14</v>
       </c>
       <c r="J41" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="K41">
         <v>14</v>
       </c>
       <c r="L41" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="M41">
         <v>14</v>
@@ -3111,7 +3094,7 @@
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C42">
         <v>20</v>
@@ -3123,31 +3106,31 @@
         <v>16</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="G42" s="2">
         <v>20</v>
       </c>
       <c r="H42" s="5" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="I42" s="5">
         <v>20</v>
       </c>
       <c r="J42" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="K42">
         <v>16</v>
       </c>
       <c r="L42" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="M42">
         <v>16</v>
       </c>
       <c r="N42" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="43" spans="1:14">
@@ -3155,43 +3138,43 @@
         <v>41</v>
       </c>
       <c r="B43" t="s">
+        <v>80</v>
+      </c>
+      <c r="C43">
+        <v>14</v>
+      </c>
+      <c r="D43" t="s">
         <v>82</v>
       </c>
-      <c r="C43">
-        <v>14</v>
-      </c>
-      <c r="D43" t="s">
-        <v>84</v>
-      </c>
       <c r="E43">
         <v>14</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="G43" s="2">
         <v>14</v>
       </c>
       <c r="H43" s="5" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="I43" s="5">
         <v>14</v>
       </c>
       <c r="J43" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="K43">
         <v>14</v>
       </c>
       <c r="L43" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="M43">
         <v>14</v>
       </c>
       <c r="N43" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="44" spans="1:14">
@@ -3199,43 +3182,43 @@
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C44">
         <v>20</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E44">
         <v>20</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="G44" s="2">
         <v>20</v>
       </c>
       <c r="H44" s="5" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="I44" s="5">
         <v>20</v>
       </c>
       <c r="J44" s="1" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="K44">
         <v>20</v>
       </c>
       <c r="L44" s="1" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="M44">
         <v>20</v>
       </c>
       <c r="N44" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="45" spans="1:14" ht="37.5">
@@ -3243,37 +3226,37 @@
         <v>43</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C45">
         <v>10</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E45">
         <v>10</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="G45" s="2">
         <v>10</v>
       </c>
       <c r="H45" s="6" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="I45" s="5">
         <v>10</v>
       </c>
       <c r="J45" s="1" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="K45">
         <v>8</v>
       </c>
       <c r="L45" s="1" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="M45">
         <v>8</v>
@@ -3284,37 +3267,37 @@
         <v>44</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C46">
         <v>10</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E46">
         <v>10</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="G46" s="2">
         <v>10</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="I46" s="5">
         <v>10</v>
       </c>
       <c r="J46" s="1" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="K46">
         <v>8</v>
       </c>
       <c r="L46" s="1" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="M46">
         <v>8</v>
@@ -3337,31 +3320,31 @@
         <v>16</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G47" s="2">
         <v>16</v>
       </c>
       <c r="H47" s="5" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="I47" s="5">
         <v>16</v>
       </c>
       <c r="J47" s="1" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="K47">
         <v>16</v>
       </c>
       <c r="L47" s="1" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="M47">
         <v>16</v>
       </c>
       <c r="N47" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="48" spans="1:14" ht="37.5">
@@ -3381,31 +3364,31 @@
         <v>16</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G48" s="2">
         <v>16</v>
       </c>
       <c r="H48" s="5" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="I48" s="5">
         <v>16</v>
       </c>
       <c r="J48" s="1" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="K48">
         <v>16</v>
       </c>
       <c r="L48" s="1" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="M48">
         <v>16</v>
       </c>
       <c r="N48" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="49" spans="1:14" ht="37.5">
@@ -3425,31 +3408,31 @@
         <v>16</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G49" s="2">
         <v>16</v>
       </c>
       <c r="H49" s="5" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="I49" s="5">
         <v>16</v>
       </c>
       <c r="J49" s="1" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="K49">
         <v>14</v>
       </c>
       <c r="L49" s="1" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="M49">
         <v>14</v>
       </c>
       <c r="N49" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="50" spans="1:14" ht="37.5">
@@ -3469,31 +3452,31 @@
         <v>16</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G50" s="2">
         <v>16</v>
       </c>
       <c r="H50" s="5" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="I50" s="5">
         <v>16</v>
       </c>
       <c r="J50" s="1" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="K50">
         <v>14</v>
       </c>
       <c r="L50" s="1" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="M50">
         <v>14</v>
       </c>
       <c r="N50" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="51" spans="1:14">
@@ -3501,37 +3484,37 @@
         <v>49</v>
       </c>
       <c r="B51" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="C51">
         <v>14</v>
       </c>
-      <c r="D51" s="1" t="s">
-        <v>139</v>
+      <c r="D51" s="7" t="s">
+        <v>232</v>
       </c>
       <c r="E51">
         <v>14</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>139</v>
+        <v>232</v>
       </c>
       <c r="G51">
         <v>14</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>139</v>
+        <v>232</v>
       </c>
       <c r="I51">
         <v>14</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>139</v>
+        <v>232</v>
       </c>
       <c r="K51">
         <v>14</v>
       </c>
       <c r="L51" s="2" t="s">
-        <v>139</v>
+        <v>232</v>
       </c>
       <c r="M51">
         <v>14</v>
@@ -3542,37 +3525,37 @@
         <v>50</v>
       </c>
       <c r="B52" t="s">
-        <v>169</v>
+        <v>233</v>
       </c>
       <c r="C52">
         <v>14</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>169</v>
+        <v>233</v>
       </c>
       <c r="E52">
         <v>14</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>169</v>
+        <v>233</v>
       </c>
       <c r="G52">
         <v>14</v>
       </c>
       <c r="H52" s="5" t="s">
-        <v>170</v>
+        <v>233</v>
       </c>
       <c r="I52">
         <v>14</v>
       </c>
       <c r="J52" s="5" t="s">
-        <v>170</v>
+        <v>233</v>
       </c>
       <c r="K52">
         <v>14</v>
       </c>
       <c r="L52" s="5" t="s">
-        <v>170</v>
+        <v>233</v>
       </c>
       <c r="M52">
         <v>14</v>
@@ -3583,37 +3566,37 @@
         <v>51</v>
       </c>
       <c r="B53" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="C53">
         <v>14</v>
       </c>
       <c r="D53" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="E53">
         <v>14</v>
       </c>
       <c r="F53" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="G53">
         <v>14</v>
       </c>
       <c r="H53" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="I53">
         <v>14</v>
       </c>
       <c r="J53" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="K53">
         <v>14</v>
       </c>
       <c r="L53" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="M53">
         <v>14</v>
@@ -3624,37 +3607,37 @@
         <v>52</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="C54">
         <v>14</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="E54">
         <v>14</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="G54">
         <v>14</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="I54">
         <v>14</v>
       </c>
       <c r="J54" s="1" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="K54">
         <v>14</v>
       </c>
       <c r="L54" s="1" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="M54">
         <v>14</v>

--- a/Assets/Originals/Excels/Button/ButtonMessage.xlsx
+++ b/Assets/Originals/Excels/Button/ButtonMessage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\Button\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10A24046-AF61-44B1-A515-9FDE63045223}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4D3F977-E95A-4FB7-B120-7D305806E5A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="236">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="249">
   <si>
     <t>number</t>
     <phoneticPr fontId="1"/>
@@ -959,6 +959,70 @@
     <rPh sb="0" eb="2">
       <t>ニホン</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>データ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Data</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>数据</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>數據</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>datos</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>dados</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>GameDatePanel内の各戻るボタン</t>
+    <rPh sb="13" eb="14">
+      <t>ナイ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>カク</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>モド</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Data Deletion</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>データ削除</t>
+    <rPh sb="3" eb="5">
+      <t>サクジョ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>删除数据</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>刪除數據</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Eliminación de datos</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Exclusão de dados</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1027,7 +1091,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1044,6 +1108,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -3647,33 +3712,126 @@
       <c r="A55">
         <v>53</v>
       </c>
+      <c r="B55" t="s">
+        <v>236</v>
+      </c>
       <c r="C55">
         <v>14</v>
       </c>
+      <c r="D55" s="1" t="s">
+        <v>237</v>
+      </c>
       <c r="E55">
         <v>14</v>
       </c>
-    </row>
-    <row r="56" spans="1:14">
+      <c r="F55" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="G55">
+        <v>14</v>
+      </c>
+      <c r="H55" t="s">
+        <v>239</v>
+      </c>
+      <c r="I55">
+        <v>14</v>
+      </c>
+      <c r="J55" t="s">
+        <v>240</v>
+      </c>
+      <c r="K55">
+        <v>14</v>
+      </c>
+      <c r="L55" t="s">
+        <v>241</v>
+      </c>
+      <c r="M55">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="56" spans="1:14" ht="37.5">
       <c r="A56">
         <v>54</v>
       </c>
+      <c r="B56" t="s">
+        <v>11</v>
+      </c>
       <c r="C56">
-        <v>14</v>
+        <v>24</v>
+      </c>
+      <c r="D56" t="s">
+        <v>12</v>
       </c>
       <c r="E56">
-        <v>14</v>
+        <v>24</v>
+      </c>
+      <c r="F56" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="G56" s="2">
+        <v>24</v>
+      </c>
+      <c r="H56" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="I56" s="5">
+        <v>24</v>
+      </c>
+      <c r="J56" t="s">
+        <v>170</v>
+      </c>
+      <c r="K56">
+        <v>24</v>
+      </c>
+      <c r="L56" t="s">
+        <v>205</v>
+      </c>
+      <c r="M56">
+        <v>24</v>
+      </c>
+      <c r="N56" s="1" t="s">
+        <v>242</v>
       </c>
     </row>
     <row r="57" spans="1:14">
       <c r="A57">
         <v>55</v>
       </c>
+      <c r="B57" t="s">
+        <v>244</v>
+      </c>
       <c r="C57">
         <v>14</v>
       </c>
+      <c r="D57" s="1" t="s">
+        <v>243</v>
+      </c>
       <c r="E57">
         <v>14</v>
+      </c>
+      <c r="F57" s="8" t="s">
+        <v>245</v>
+      </c>
+      <c r="G57">
+        <v>14</v>
+      </c>
+      <c r="H57" t="s">
+        <v>246</v>
+      </c>
+      <c r="I57">
+        <v>14</v>
+      </c>
+      <c r="J57" t="s">
+        <v>247</v>
+      </c>
+      <c r="K57">
+        <v>12</v>
+      </c>
+      <c r="L57" t="s">
+        <v>248</v>
+      </c>
+      <c r="M57">
+        <v>12</v>
       </c>
     </row>
     <row r="58" spans="1:14">

--- a/Assets/Originals/Excels/Button/ButtonMessage.xlsx
+++ b/Assets/Originals/Excels/Button/ButtonMessage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\Button\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4D3F977-E95A-4FB7-B120-7D305806E5A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2AE877A-21A3-49D5-9151-10ECE7F69722}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="249">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="250">
   <si>
     <t>number</t>
     <phoneticPr fontId="1"/>
@@ -1023,6 +1023,13 @@
   </si>
   <si>
     <t>Exclusão de dados</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ReallyDeleteSavePanel内</t>
+    <rPh sb="21" eb="22">
+      <t>ナイ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -3838,22 +3845,88 @@
       <c r="A58">
         <v>56</v>
       </c>
+      <c r="B58" t="s">
+        <v>45</v>
+      </c>
       <c r="C58">
         <v>14</v>
       </c>
+      <c r="D58" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="E58">
         <v>14</v>
+      </c>
+      <c r="F58" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="G58" s="2">
+        <v>14</v>
+      </c>
+      <c r="H58" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="I58" s="5">
+        <v>14</v>
+      </c>
+      <c r="J58" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="K58">
+        <v>14</v>
+      </c>
+      <c r="L58" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="M58">
+        <v>14</v>
+      </c>
+      <c r="N58" s="1" t="s">
+        <v>249</v>
       </c>
     </row>
     <row r="59" spans="1:14">
       <c r="A59">
         <v>57</v>
       </c>
+      <c r="B59" t="s">
+        <v>46</v>
+      </c>
       <c r="C59">
         <v>14</v>
       </c>
+      <c r="D59" s="1" t="s">
+        <v>48</v>
+      </c>
       <c r="E59">
         <v>14</v>
+      </c>
+      <c r="F59" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="G59" s="2">
+        <v>14</v>
+      </c>
+      <c r="H59" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="I59" s="5">
+        <v>14</v>
+      </c>
+      <c r="J59" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="K59">
+        <v>14</v>
+      </c>
+      <c r="L59" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="M59">
+        <v>14</v>
+      </c>
+      <c r="N59" s="1" t="s">
+        <v>249</v>
       </c>
     </row>
     <row r="60" spans="1:14">
